--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_30sep26_Wed.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_30sep26_Wed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\python\stocks\ORDER_MGMT\regular_order_mgmt\order_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED60DB01-DDAE-4CA8-B15B-7CA07F5A65B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A561A7F1-B750-46DF-884F-746AC8EDE0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3491" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3492" uniqueCount="319">
   <si>
     <t>Date</t>
   </si>
@@ -1154,7 +1154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1311,20 +1311,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1725,7 +1743,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B2, $C$2:$C$692, C2, $D$2:$D$692, D2, $E$2:$E$692, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$692, B2, $C$2:$C$692, C2, $D$2:$D$692, D2, $E$2:$E$692, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -1764,7 +1782,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B3, $C$2:$C$692, C3, $D$2:$D$692, D3, $E$2:$E$692, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1801,7 +1819,7 @@
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
       <c r="N4" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B4, $C$2:$C$692, C4, $D$2:$D$692, D4, $E$2:$E$692, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1840,7 +1858,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B5, $C$2:$C$692, C5, $D$2:$D$692, D5, $E$2:$E$692, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1879,7 +1897,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B6, $C$2:$C$692, C6, $D$2:$D$692, D6, $E$2:$E$692, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -1925,7 +1943,7 @@
         <v>10880</v>
       </c>
       <c r="N7" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B7, $C$2:$C$692, C7, $D$2:$D$692, D7, $E$2:$E$692, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -1966,7 +1984,7 @@
       <c r="L8" s="17"/>
       <c r="M8" s="17"/>
       <c r="N8" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B8, $C$2:$C$692, C8, $D$2:$D$692, D8, $E$2:$E$692, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2012,7 +2030,7 @@
         <v>10680</v>
       </c>
       <c r="N9" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B9, $C$2:$C$692, C9, $D$2:$D$692, D9, $E$2:$E$692, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="10"/>
@@ -2053,7 +2071,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B10, $C$2:$C$692, C10, $D$2:$D$692, D10, $E$2:$E$692, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2092,7 +2110,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B11, $C$2:$C$692, C11, $D$2:$D$692, D11, $E$2:$E$692, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2129,7 +2147,7 @@
       <c r="L12" s="17"/>
       <c r="M12" s="17"/>
       <c r="N12" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B12, $C$2:$C$692, C12, $D$2:$D$692, D12, $E$2:$E$692, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2166,7 +2184,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B13, $C$2:$C$692, C13, $D$2:$D$692, D13, $E$2:$E$692, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2203,7 +2221,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B14, $C$2:$C$692, C14, $D$2:$D$692, D14, $E$2:$E$692, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2243,7 +2261,7 @@
         <v>3156</v>
       </c>
       <c r="N15" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B15, $C$2:$C$692, C15, $D$2:$D$692, D15, $E$2:$E$692, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P15" s="19"/>
@@ -2281,7 +2299,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B16, $C$2:$C$692, C16, $D$2:$D$692, D16, $E$2:$E$692, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16"/>
@@ -2320,7 +2338,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B17, $C$2:$C$692, C17, $D$2:$D$692, D17, $E$2:$E$692, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17"/>
@@ -2359,7 +2377,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B18, $C$2:$C$692, C18, $D$2:$D$692, D18, $E$2:$E$692, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O18"/>
@@ -2407,7 +2425,7 @@
         <v>240</v>
       </c>
       <c r="N19" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B19, $C$2:$C$692, C19, $D$2:$D$692, D19, $E$2:$E$692, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2444,7 +2462,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B20, $C$2:$C$692, C20, $D$2:$D$692, D20, $E$2:$E$692, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
@@ -2483,7 +2501,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B21, $C$2:$C$692, C21, $D$2:$D$692, D21, $E$2:$E$692, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21"/>
@@ -2522,7 +2540,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="17"/>
       <c r="N22" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B22, $C$2:$C$692, C22, $D$2:$D$692, D22, $E$2:$E$692, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O22"/>
@@ -2565,7 +2583,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B23, $C$2:$C$692, C23, $D$2:$D$692, D23, $E$2:$E$692, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
@@ -2606,7 +2624,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B24, $C$2:$C$692, C24, $D$2:$D$692, D24, $E$2:$E$692, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -2654,7 +2672,7 @@
         <v>554</v>
       </c>
       <c r="N25" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B25, $C$2:$C$692, C25, $D$2:$D$692, D25, $E$2:$E$692, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2691,7 +2709,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B26, $C$2:$C$692, C26, $D$2:$D$692, D26, $E$2:$E$692, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -2730,7 +2748,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B27, $C$2:$C$692, C27, $D$2:$D$692, D27, $E$2:$E$692, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O27"/>
@@ -2778,7 +2796,7 @@
         <v>295</v>
       </c>
       <c r="N28" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B28, $C$2:$C$692, C28, $D$2:$D$692, D28, $E$2:$E$692, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2817,7 +2835,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
       <c r="N29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B29, $C$2:$C$692, C29, $D$2:$D$692, D29, $E$2:$E$692, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O29"/>
@@ -2866,7 +2884,7 @@
         <v>540</v>
       </c>
       <c r="N30" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B30, $C$2:$C$692, C30, $D$2:$D$692, D30, $E$2:$E$692, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -2915,7 +2933,7 @@
         <v>225</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B31, $C$2:$C$692, C31, $D$2:$D$692, D31, $E$2:$E$692, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -2961,7 +2979,7 @@
         <v>300</v>
       </c>
       <c r="N32" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B32, $C$2:$C$692, C32, $D$2:$D$692, D32, $E$2:$E$692, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O32"/>
@@ -3002,7 +3020,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="17"/>
       <c r="N33" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B33, $C$2:$C$692, C33, $D$2:$D$692, D33, $E$2:$E$692, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33"/>
@@ -3050,7 +3068,7 @@
         <v>314</v>
       </c>
       <c r="N34" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B34, $C$2:$C$692, C34, $D$2:$D$692, D34, $E$2:$E$692, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3089,7 +3107,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B35, $C$2:$C$692, C35, $D$2:$D$692, D35, $E$2:$E$692, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3128,7 +3146,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B36, $C$2:$C$692, C36, $D$2:$D$692, D36, $E$2:$E$692, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -3167,7 +3185,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B37, $C$2:$C$692, C37, $D$2:$D$692, D37, $E$2:$E$692, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -3208,7 +3226,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B38, $C$2:$C$692, C38, $D$2:$D$692, D38, $E$2:$E$692, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -3246,7 +3264,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B39, $C$2:$C$692, C39, $D$2:$D$692, D39, $E$2:$E$692, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -3284,7 +3302,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="17"/>
       <c r="N40" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B40, $C$2:$C$692, C40, $D$2:$D$692, D40, $E$2:$E$692, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O40"/>
@@ -3325,7 +3343,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B41, $C$2:$C$692, C41, $D$2:$D$692, D41, $E$2:$E$692, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -3366,7 +3384,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B42, $C$2:$C$692, C42, $D$2:$D$692, D42, $E$2:$E$692, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P42"/>
@@ -3413,7 +3431,7 @@
         <v>646</v>
       </c>
       <c r="N43" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B43, $C$2:$C$692, C43, $D$2:$D$692, D43, $E$2:$E$692, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3452,7 +3470,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B44, $C$2:$C$692, C44, $D$2:$D$692, D44, $E$2:$E$692, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -3500,7 +3518,7 @@
         <v>300</v>
       </c>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B45, $C$2:$C$692, C45, $D$2:$D$692, D45, $E$2:$E$692, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45" s="10"/>
@@ -3541,7 +3559,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B46, $C$2:$C$692, C46, $D$2:$D$692, D46, $E$2:$E$692, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3580,7 +3598,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B47, $C$2:$C$692, C47, $D$2:$D$692, D47, $E$2:$E$692, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -3614,7 +3632,7 @@
       <c r="I48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J48" s="55" t="s">
+      <c r="J48" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K48" s="18" t="s">
@@ -3628,7 +3646,7 @@
         <v>300</v>
       </c>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B48, $C$2:$C$692, C48, $D$2:$D$692, D48, $E$2:$E$692, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O48" s="10"/>
@@ -3662,7 +3680,7 @@
       <c r="I49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J49" s="55" t="s">
+      <c r="J49" s="18" t="s">
         <v>55</v>
       </c>
       <c r="K49" s="18" t="s">
@@ -3676,7 +3694,7 @@
         <v>516</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B49, $C$2:$C$692, C49, $D$2:$D$692, D49, $E$2:$E$692, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O49" s="10"/>
@@ -3710,12 +3728,12 @@
       <c r="I50" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J50" s="54"/>
+      <c r="J50" s="51"/>
       <c r="K50" s="17"/>
       <c r="L50" s="17"/>
       <c r="M50" s="17"/>
       <c r="N50" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B50, $C$2:$C$692, C50, $D$2:$D$692, D50, $E$2:$E$692, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P50" s="10"/>
@@ -3748,12 +3766,12 @@
       <c r="I51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="54"/>
+      <c r="J51" s="51"/>
       <c r="K51" s="17"/>
       <c r="L51" s="17"/>
       <c r="M51" s="17"/>
       <c r="N51" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B51, $C$2:$C$692, C51, $D$2:$D$692, D51, $E$2:$E$692, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -3785,14 +3803,14 @@
       <c r="I52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="54" t="s">
+      <c r="J52" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K52" s="17"/>
       <c r="L52" s="17"/>
       <c r="M52" s="17"/>
       <c r="N52" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B52, $C$2:$C$692, C52, $D$2:$D$692, D52, $E$2:$E$692, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="10"/>
@@ -3826,7 +3844,7 @@
       <c r="I53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J53" s="55" t="s">
+      <c r="J53" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K53" s="18" t="s">
@@ -3840,7 +3858,7 @@
         <v>350</v>
       </c>
       <c r="N53" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B53, $C$2:$C$692, C53, $D$2:$D$692, D53, $E$2:$E$692, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O53" s="10"/>
@@ -3874,14 +3892,14 @@
       <c r="I54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J54" s="54" t="s">
+      <c r="J54" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K54" s="17"/>
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B54, $C$2:$C$692, C54, $D$2:$D$692, D54, $E$2:$E$692, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -3915,14 +3933,14 @@
       <c r="I55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J55" s="57" t="s">
+      <c r="J55" s="55" t="s">
         <v>55</v>
       </c>
       <c r="K55" s="17"/>
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B55, $C$2:$C$692, C55, $D$2:$D$692, D55, $E$2:$E$692, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -3956,7 +3974,7 @@
       <c r="I56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J56" s="55" t="s">
+      <c r="J56" s="18" t="s">
         <v>55</v>
       </c>
       <c r="K56" s="18" t="s">
@@ -3970,7 +3988,7 @@
         <v>500</v>
       </c>
       <c r="N56" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B56, $C$2:$C$692, C56, $D$2:$D$692, D56, $E$2:$E$692, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56" s="10"/>
@@ -4004,12 +4022,12 @@
       <c r="I57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="54"/>
+      <c r="J57" s="51"/>
       <c r="K57" s="17"/>
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B57, $C$2:$C$692, C57, $D$2:$D$692, D57, $E$2:$E$692, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4041,12 +4059,12 @@
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="54"/>
+      <c r="J58" s="51"/>
       <c r="K58" s="17"/>
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B58, $C$2:$C$692, C58, $D$2:$D$692, D58, $E$2:$E$692, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4078,62 +4096,62 @@
       <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="54" t="s">
+      <c r="J59" s="51" t="s">
         <v>55</v>
       </c>
       <c r="K59" s="17"/>
       <c r="L59" s="17"/>
       <c r="M59" s="17"/>
       <c r="N59" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B59, $C$2:$C$692, C59, $D$2:$D$692, D59, $E$2:$E$692, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59"/>
       <c r="P59"/>
     </row>
-    <row r="60" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="49">
+    <row r="60" spans="1:16" s="63" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A60" s="57">
         <v>46293.393055555556</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="5">
+      <c r="C60" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D60" s="59">
         <v>1</v>
       </c>
-      <c r="E60" s="5">
+      <c r="E60" s="59">
         <v>20200</v>
       </c>
-      <c r="F60" s="4">
+      <c r="F60" s="60">
         <v>2.7989821880000001</v>
       </c>
-      <c r="G60" s="2" t="s">
+      <c r="G60" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="H60" s="5">
+      <c r="H60" s="59">
         <v>19650</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J60" s="18" t="s">
+      <c r="I60" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J60" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="K60" s="18" t="s">
+      <c r="K60" s="62" t="s">
         <v>305</v>
       </c>
-      <c r="L60" s="18">
+      <c r="L60" s="62">
         <v>19550</v>
       </c>
-      <c r="M60" s="18">
+      <c r="M60" s="62">
         <f>ABS((D60*E60)-L60)</f>
         <v>650</v>
       </c>
-      <c r="N60" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B60, $C$2:$C$692, C60, $D$2:$D$692, D60, $E$2:$E$692, E60) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="N60" s="63" t="str">
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4165,14 +4183,14 @@
       <c r="I61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="54" t="s">
+      <c r="J61" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K61" s="17"/>
       <c r="L61" s="17"/>
       <c r="M61" s="17"/>
       <c r="N61" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B61, $C$2:$C$692, C61, $D$2:$D$692, D61, $E$2:$E$692, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61"/>
@@ -4206,12 +4224,12 @@
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="54"/>
+      <c r="J62" s="51"/>
       <c r="K62" s="17"/>
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B62, $C$2:$C$692, C62, $D$2:$D$692, D62, $E$2:$E$692, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62" s="19"/>
@@ -4244,18 +4262,18 @@
       <c r="I63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J63" s="58" t="s">
+      <c r="J63" s="56" t="s">
         <v>41</v>
       </c>
       <c r="K63" s="17"/>
       <c r="L63" s="17"/>
       <c r="M63" s="17"/>
       <c r="N63" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B63, $C$2:$C$692, C63, $D$2:$D$692, D63, $E$2:$E$692, E63) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" s="24" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" s="24" customFormat="1" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="3">
         <v>46267.375</v>
       </c>
@@ -4297,7 +4315,7 @@
         <v>360</v>
       </c>
       <c r="N64" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B64, $C$2:$C$692, C64, $D$2:$D$692, D64, $E$2:$E$692, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64" s="38" t="s">
@@ -4347,7 +4365,7 @@
         <v>500</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B65, $C$2:$C$692, C65, $D$2:$D$692, D65, $E$2:$E$692, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4379,61 +4397,61 @@
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="54" t="s">
+      <c r="J66" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K66" s="17"/>
       <c r="L66" s="17"/>
       <c r="M66" s="17"/>
       <c r="N66" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B66, $C$2:$C$692, C66, $D$2:$D$692, D66, $E$2:$E$692, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$692, B66, $C$2:$C$692, C66, $D$2:$D$692, D66, $E$2:$E$692, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P66" s="25"/>
     </row>
-    <row r="67" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A67" s="49">
+    <row r="67" spans="1:16" s="63" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A67" s="57">
         <v>46293.375</v>
       </c>
-      <c r="B67" s="2" t="s">
+      <c r="B67" s="58" t="s">
         <v>66</v>
       </c>
-      <c r="C67" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="5">
+      <c r="C67" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" s="59">
         <v>10</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E67" s="59">
         <v>1166</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="60">
         <v>4.1071428570000004</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="G67" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="H67" s="5">
+      <c r="H67" s="59">
         <v>1120</v>
       </c>
-      <c r="I67" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J67" s="18" t="s">
+      <c r="I67" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J67" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="K67" s="18" t="s">
+      <c r="K67" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="L67" s="18">
+      <c r="L67" s="62">
         <v>11360</v>
       </c>
-      <c r="M67" s="18">
+      <c r="M67" s="62">
         <f>ABS((D67*E67)-L67)</f>
         <v>300</v>
       </c>
-      <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B67, $C$2:$C$692, C67, $D$2:$D$692, D67, $E$2:$E$692, E67) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="N67" s="63" t="str">
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4465,12 +4483,12 @@
       <c r="I68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J68" s="54"/>
+      <c r="J68" s="51"/>
       <c r="K68" s="17"/>
       <c r="L68" s="17"/>
       <c r="M68" s="17"/>
       <c r="N68" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B68, $C$2:$C$692, C68, $D$2:$D$692, D68, $E$2:$E$692, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="25"/>
@@ -4513,11 +4531,11 @@
         <v>3560</v>
       </c>
       <c r="M69" s="18">
-        <f>ABS((D69*E69)-L69)</f>
+        <f t="shared" ref="M69:M77" si="2">ABS((D69*E69)-L69)</f>
         <v>250</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B69, $C$2:$C$692, C69, $D$2:$D$692, D69, $E$2:$E$692, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69" s="10"/>
@@ -4561,11 +4579,11 @@
         <v>10250</v>
       </c>
       <c r="M70" s="18">
-        <f>ABS((D70*E70)-L70)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N70" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B70, $C$2:$C$692, C70, $D$2:$D$692, D70, $E$2:$E$692, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4607,11 +4625,11 @@
         <v>39300</v>
       </c>
       <c r="M71" s="18">
-        <f>ABS((D71*E71)-L71)</f>
+        <f t="shared" si="2"/>
         <v>18850</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B71, $C$2:$C$692, C71, $D$2:$D$692, D71, $E$2:$E$692, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4653,15 +4671,15 @@
         <v>4510</v>
       </c>
       <c r="M72" s="18">
-        <f>ABS((D72*E72)-L72)</f>
+        <f t="shared" si="2"/>
         <v>288</v>
       </c>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B72, $C$2:$C$692, C72, $D$2:$D$692, D72, $E$2:$E$692, E72) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="3">
         <v>46268.375</v>
       </c>
@@ -4699,64 +4717,64 @@
         <v>32200</v>
       </c>
       <c r="M73" s="18">
-        <f>ABS((D73*E73)-L73)</f>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B73, $C$2:$C$692, C73, $D$2:$D$692, D73, $E$2:$E$692, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O73" s="38" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="74" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A74" s="3">
+    <row r="74" spans="1:16" s="63" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="64">
         <v>46262.375</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="61" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="4">
+      <c r="C74" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" s="60">
         <v>2</v>
       </c>
-      <c r="E74" s="4">
+      <c r="E74" s="60">
         <v>4360</v>
       </c>
-      <c r="F74" s="4">
+      <c r="F74" s="60">
         <v>5.5690072639999997</v>
       </c>
-      <c r="G74" s="2" t="s">
+      <c r="G74" s="58" t="s">
         <v>83</v>
       </c>
-      <c r="H74" s="5">
+      <c r="H74" s="59">
         <v>4130</v>
       </c>
-      <c r="I74" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J74" s="18" t="s">
+      <c r="I74" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J74" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="K74" s="18" t="s">
+      <c r="K74" s="62" t="s">
         <v>187</v>
       </c>
-      <c r="L74" s="18">
+      <c r="L74" s="62">
         <v>8420</v>
       </c>
-      <c r="M74" s="18">
-        <f>ABS((D74*E74)-L74)</f>
+      <c r="M74" s="62">
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
-      <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B74, $C$2:$C$692, C74, $D$2:$D$692, D74, $E$2:$E$692, E74) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N74" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="3">
         <v>46281.376388888886</v>
       </c>
@@ -4794,11 +4812,11 @@
         <v>4640</v>
       </c>
       <c r="M75" s="18">
-        <f>ABS((D75*E75)-L75)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B75, $C$2:$C$692, C75, $D$2:$D$692, D75, $E$2:$E$692, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="38" t="s">
@@ -4844,11 +4862,11 @@
         <v>3300</v>
       </c>
       <c r="M76" s="18">
-        <f>ABS((D76*E76)-L76)</f>
+        <f t="shared" si="2"/>
         <v>250</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B76, $C$2:$C$692, C76, $D$2:$D$692, D76, $E$2:$E$692, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="10"/>
@@ -4882,7 +4900,7 @@
       <c r="I77" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J77" s="55" t="s">
+      <c r="J77" s="18" t="s">
         <v>41</v>
       </c>
       <c r="K77" s="18" t="s">
@@ -4892,11 +4910,11 @@
         <v>56375</v>
       </c>
       <c r="M77" s="18">
-        <f>ABS((D77*E77)-L77)</f>
+        <f t="shared" si="2"/>
         <v>34175</v>
       </c>
       <c r="N77" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B77, $C$2:$C$692, C77, $D$2:$D$692, D77, $E$2:$E$692, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4932,7 +4950,7 @@
         <v>118</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B78, $C$2:$C$692, C78, $D$2:$D$692, D78, $E$2:$E$692, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -4974,11 +4992,11 @@
         <v>10400</v>
       </c>
       <c r="M79" s="18">
-        <f>ABS((D79*E79)-L79)</f>
+        <f t="shared" ref="M79:M89" si="3">ABS((D79*E79)-L79)</f>
         <v>300</v>
       </c>
       <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B79, $C$2:$C$692, C79, $D$2:$D$692, D79, $E$2:$E$692, E79) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5020,15 +5038,15 @@
         <v>8320</v>
       </c>
       <c r="M80" s="18">
-        <f>ABS((D80*E80)-L80)</f>
+        <f t="shared" si="3"/>
         <v>650</v>
       </c>
       <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B80, $C$2:$C$692, C80, $D$2:$D$692, D80, $E$2:$E$692, E80) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="3">
         <v>46274.375</v>
       </c>
@@ -5066,11 +5084,11 @@
         <v>11660</v>
       </c>
       <c r="M81" s="18">
-        <f>ABS((D81*E81)-L81)</f>
+        <f t="shared" si="3"/>
         <v>300</v>
       </c>
       <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B81, $C$2:$C$692, C81, $D$2:$D$692, D81, $E$2:$E$692, E81) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O81" s="38" t="s">
@@ -5115,11 +5133,11 @@
         <v>35200</v>
       </c>
       <c r="M82" s="18">
-        <f>ABS((D82*E82)-L82)</f>
+        <f t="shared" si="3"/>
         <v>720</v>
       </c>
       <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B82, $C$2:$C$692, C82, $D$2:$D$692, D82, $E$2:$E$692, E82) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5161,11 +5179,11 @@
         <v>32900</v>
       </c>
       <c r="M83" s="18">
-        <f>ABS((D83*E83)-L83)</f>
+        <f t="shared" si="3"/>
         <v>1000</v>
       </c>
       <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B83, $C$2:$C$692, C83, $D$2:$D$692, D83, $E$2:$E$692, E83) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5207,11 +5225,11 @@
         <v>16755</v>
       </c>
       <c r="M84" s="18">
-        <f>ABS((D84*E84)-L84)</f>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B84, $C$2:$C$692, C84, $D$2:$D$692, D84, $E$2:$E$692, E84) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5253,15 +5271,15 @@
         <v>5450</v>
       </c>
       <c r="M85" s="18">
-        <f>ABS((D85*E85)-L85)</f>
+        <f t="shared" si="3"/>
         <v>295</v>
       </c>
       <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B85, $C$2:$C$692, C85, $D$2:$D$692, D85, $E$2:$E$692, E85) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A86" s="3">
         <v>46286.468055555553</v>
       </c>
@@ -5299,11 +5317,11 @@
         <v>6367.2</v>
       </c>
       <c r="M86" s="18">
-        <f>ABS((D86*E86)-L86)</f>
+        <f t="shared" si="3"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B86, $C$2:$C$692, C86, $D$2:$D$692, D86, $E$2:$E$692, E86) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O86" s="38" t="s">
@@ -5349,11 +5367,11 @@
         <v>8870</v>
       </c>
       <c r="M87" s="18">
-        <f>ABS((D87*E87)-L87)</f>
+        <f t="shared" si="3"/>
         <v>200</v>
       </c>
       <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B87, $C$2:$C$692, C87, $D$2:$D$692, D87, $E$2:$E$692, E87) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O87" s="10"/>
@@ -5397,57 +5415,57 @@
         <v>39300</v>
       </c>
       <c r="M88" s="18">
-        <f>ABS((D88*E88)-L88)</f>
+        <f t="shared" si="3"/>
         <v>18350</v>
       </c>
       <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B88, $C$2:$C$692, C88, $D$2:$D$692, D88, $E$2:$E$692, E88) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A89" s="3">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" s="63" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="64">
         <v>46290.385416666664</v>
       </c>
-      <c r="B89" s="2" t="s">
+      <c r="B89" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="5">
+      <c r="C89" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D89" s="59">
         <v>200</v>
       </c>
-      <c r="E89" s="5">
-        <v>33.49</v>
-      </c>
-      <c r="F89" s="4">
+      <c r="E89" s="59">
+        <v>32.49</v>
+      </c>
+      <c r="F89" s="60">
         <v>8.2067851370000007</v>
       </c>
-      <c r="G89" s="2" t="s">
+      <c r="G89" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="H89" s="5">
+      <c r="H89" s="59">
         <v>30.95</v>
       </c>
-      <c r="I89" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="18" t="s">
+      <c r="I89" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="K89" s="18" t="s">
+      <c r="K89" s="62" t="s">
         <v>304</v>
       </c>
-      <c r="L89" s="18">
+      <c r="L89" s="62">
         <v>6202</v>
       </c>
-      <c r="M89" s="18">
-        <f>ABS((D89*E89)-L89)</f>
-        <v>496</v>
-      </c>
-      <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B89, $C$2:$C$692, C89, $D$2:$D$692, D89, $E$2:$E$692, E89) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="M89" s="62">
+        <f t="shared" si="3"/>
+        <v>296</v>
+      </c>
+      <c r="N89" s="63" t="str">
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5483,57 +5501,57 @@
         <v>118</v>
       </c>
       <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B90, $C$2:$C$692, C90, $D$2:$D$692, D90, $E$2:$E$692, E90) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="3">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" s="63" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A91" s="64">
         <v>46287.375</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="C91" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="4">
+      <c r="C91" s="61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D91" s="60">
         <v>25</v>
       </c>
-      <c r="E91" s="4">
+      <c r="E91" s="60">
         <v>348</v>
       </c>
-      <c r="F91" s="4">
+      <c r="F91" s="60">
         <v>8.411214953</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="G91" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="H91" s="5">
+      <c r="H91" s="59">
         <v>321</v>
       </c>
-      <c r="I91" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="18" t="s">
+      <c r="I91" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J91" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="K91" s="18" t="s">
+      <c r="K91" s="62" t="s">
         <v>295</v>
       </c>
-      <c r="L91" s="18">
+      <c r="L91" s="62">
         <v>8400</v>
       </c>
-      <c r="M91" s="18">
-        <f>ABS((D91*E91)-L91)</f>
+      <c r="M91" s="62">
+        <f t="shared" ref="M91:M102" si="4">ABS((D91*E91)-L91)</f>
         <v>300</v>
       </c>
-      <c r="N91" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B91, $C$2:$C$692, C91, $D$2:$D$692, D91, $E$2:$E$692, E91) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="N91" s="63" t="str">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A92" s="40">
         <v>46273.375</v>
       </c>
@@ -5571,18 +5589,18 @@
         <v>19730.5</v>
       </c>
       <c r="M92" s="27">
-        <f>ABS((D92*E92)-L92)</f>
+        <f t="shared" si="4"/>
         <v>504.5</v>
       </c>
       <c r="N92" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B92, $C$2:$C$692, C92, $D$2:$D$692, D92, $E$2:$E$692, E92) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O92" s="38" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="93" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A93" s="30">
         <v>46274.375</v>
       </c>
@@ -5620,11 +5638,11 @@
         <v>19690</v>
       </c>
       <c r="M93" s="27">
-        <f>ABS((D93*E93)-L93)</f>
+        <f t="shared" si="4"/>
         <v>545</v>
       </c>
       <c r="N93" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B93, $C$2:$C$692, C93, $D$2:$D$692, D93, $E$2:$E$692, E93) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O93" s="38" t="s">
@@ -5632,7 +5650,7 @@
       </c>
       <c r="P93" s="29"/>
     </row>
-    <row r="94" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A94" s="30">
         <v>46267.425694444442</v>
       </c>
@@ -5670,11 +5688,11 @@
         <v>4120</v>
       </c>
       <c r="M94" s="27">
-        <f>ABS((D94*E94)-L94)</f>
+        <f t="shared" si="4"/>
         <v>270</v>
       </c>
       <c r="N94" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B94, $C$2:$C$692, C94, $D$2:$D$692, D94, $E$2:$E$692, E94) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O94" s="39" t="s">
@@ -5682,7 +5700,7 @@
       </c>
       <c r="P94" s="29"/>
     </row>
-    <row r="95" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A95" s="30">
         <v>46280.593055555553</v>
       </c>
@@ -5720,11 +5738,11 @@
         <v>2006.3999999999999</v>
       </c>
       <c r="M95" s="27">
-        <f>ABS((D95*E95)-L95)</f>
+        <f t="shared" si="4"/>
         <v>188.60000000000014</v>
       </c>
       <c r="N95" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B95, $C$2:$C$692, C95, $D$2:$D$692, D95, $E$2:$E$692, E95) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O95" s="39" t="s">
@@ -5770,11 +5788,11 @@
         <v>3400</v>
       </c>
       <c r="M96" s="18">
-        <f>ABS((D96*E96)-L96)</f>
+        <f t="shared" si="4"/>
         <v>250</v>
       </c>
       <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B96, $C$2:$C$692, C96, $D$2:$D$692, D96, $E$2:$E$692, E96) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5816,11 +5834,11 @@
         <v>33200</v>
       </c>
       <c r="M97" s="18">
-        <f>ABS((D97*E97)-L97)</f>
+        <f t="shared" si="4"/>
         <v>1200</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B97, $C$2:$C$692, C97, $D$2:$D$692, D97, $E$2:$E$692, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -5862,15 +5880,15 @@
         <v>14130</v>
       </c>
       <c r="M98" s="18">
-        <f>ABS((D98*E98)-L98)</f>
+        <f t="shared" si="4"/>
         <v>714</v>
       </c>
       <c r="N98" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B98, $C$2:$C$692, C98, $D$2:$D$692, D98, $E$2:$E$692, E98) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="99" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A99" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -5908,18 +5926,18 @@
         <v>15075</v>
       </c>
       <c r="M99" s="18">
-        <f>ABS((D99*E99)-L99)</f>
+        <f t="shared" si="4"/>
         <v>645</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B99, $C$2:$C$692, C99, $D$2:$D$692, D99, $E$2:$E$692, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O99" s="38" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="100" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A100" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -5947,7 +5965,7 @@
       <c r="I100" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="55" t="s">
+      <c r="J100" s="18" t="s">
         <v>117</v>
       </c>
       <c r="K100" s="18" t="s">
@@ -5957,18 +5975,18 @@
         <v>8480</v>
       </c>
       <c r="M100" s="26">
-        <f>ABS((D100*E100)-L100)</f>
+        <f t="shared" si="4"/>
         <v>280</v>
       </c>
       <c r="N100" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B100, $C$2:$C$692, C100, $D$2:$D$692, D100, $E$2:$E$692, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O100" s="38" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="101" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A101" s="3">
         <v>46280.375694444447</v>
       </c>
@@ -6006,11 +6024,11 @@
         <v>10249</v>
       </c>
       <c r="M101" s="18">
-        <f>ABS((D101*E101)-L101)</f>
+        <f t="shared" si="4"/>
         <v>4451</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B101, $C$2:$C$692, C101, $D$2:$D$692, D101, $E$2:$E$692, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="38" t="s">
@@ -6056,15 +6074,15 @@
         <v>8870</v>
       </c>
       <c r="M102" s="18">
-        <f>ABS((D102*E102)-L102)</f>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B102, $C$2:$C$692, C102, $D$2:$D$692, D102, $E$2:$E$692, E102) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="103" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A103" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -6094,7 +6112,7 @@
       </c>
       <c r="J103" s="34"/>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B103, $C$2:$C$692, C103, $D$2:$D$692, D103, $E$2:$E$692, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O103" s="38" t="s">
@@ -6140,11 +6158,11 @@
         <v>4200</v>
       </c>
       <c r="M104" s="18">
-        <f>ABS((D104*E104)-L104)</f>
+        <f t="shared" ref="M104:M114" si="5">ABS((D104*E104)-L104)</f>
         <v>290</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B104, $C$2:$C$692, C104, $D$2:$D$692, D104, $E$2:$E$692, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6186,17 +6204,17 @@
         <v>20010</v>
       </c>
       <c r="M105" s="18">
-        <f>ABS((D105*E105)-L105)</f>
+        <f t="shared" si="5"/>
         <v>450</v>
       </c>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B105, $C$2:$C$692, C105, $D$2:$D$692, D105, $E$2:$E$692, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="10"/>
       <c r="P105"/>
     </row>
-    <row r="106" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A106" s="11">
         <v>46243.375</v>
       </c>
@@ -6234,11 +6252,11 @@
         <v>8570</v>
       </c>
       <c r="M106" s="27">
-        <f>ABS((D106*E106)-L106)</f>
+        <f t="shared" si="5"/>
         <v>650</v>
       </c>
       <c r="N106" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B106, $C$2:$C$692, C106, $D$2:$D$692, D106, $E$2:$E$692, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O106" s="38" t="s">
@@ -6246,7 +6264,7 @@
       </c>
       <c r="P106" s="10"/>
     </row>
-    <row r="107" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="30">
         <v>46265.375694444447</v>
       </c>
@@ -6284,18 +6302,18 @@
         <v>5520</v>
       </c>
       <c r="M107" s="27">
-        <f>ABS((D107*E107)-L107)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N107" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B107, $C$2:$C$692, C107, $D$2:$D$692, D107, $E$2:$E$692, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="38" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="108" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A108" s="40">
         <v>46243.505555555559</v>
       </c>
@@ -6333,18 +6351,18 @@
         <v>2657</v>
       </c>
       <c r="M108" s="27">
-        <f>ABS((D108*E108)-L108)</f>
+        <f t="shared" si="5"/>
         <v>253</v>
       </c>
       <c r="N108" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B108, $C$2:$C$692, C108, $D$2:$D$692, D108, $E$2:$E$692, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O108" s="38" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A109" s="30">
         <v>46280.588194444441</v>
       </c>
@@ -6382,11 +6400,11 @@
         <v>2554.5</v>
       </c>
       <c r="M109" s="27">
-        <f>ABS((D109*E109)-L109)</f>
+        <f t="shared" si="5"/>
         <v>355.5</v>
       </c>
       <c r="N109" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B109, $C$2:$C$692, C109, $D$2:$D$692, D109, $E$2:$E$692, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Duplicate</v>
       </c>
       <c r="O109" s="38" t="s">
@@ -6394,49 +6412,49 @@
       </c>
       <c r="P109" s="29"/>
     </row>
-    <row r="110" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A110" s="49">
+    <row r="110" spans="1:16" s="63" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A110" s="57">
         <v>46289.390277777777</v>
       </c>
-      <c r="B110" s="2" t="s">
+      <c r="B110" s="58" t="s">
         <v>59</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D110" s="5">
+      <c r="C110" s="58" t="s">
+        <v>7</v>
+      </c>
+      <c r="D110" s="59">
         <v>10</v>
       </c>
-      <c r="E110" s="5">
+      <c r="E110" s="59">
         <v>1054</v>
       </c>
-      <c r="F110" s="4">
+      <c r="F110" s="60">
         <v>9.8603293730000008</v>
       </c>
-      <c r="G110" s="2" t="s">
+      <c r="G110" s="58" t="s">
         <v>60</v>
       </c>
-      <c r="H110" s="5">
+      <c r="H110" s="59">
         <v>959.4</v>
       </c>
-      <c r="I110" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J110" s="18" t="s">
+      <c r="I110" s="61" t="s">
+        <v>8</v>
+      </c>
+      <c r="J110" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="K110" s="18" t="s">
+      <c r="K110" s="62" t="s">
         <v>298</v>
       </c>
-      <c r="L110" s="18">
+      <c r="L110" s="62">
         <v>9886</v>
       </c>
-      <c r="M110" s="18">
-        <f>ABS((D110*E110)-L110)</f>
+      <c r="M110" s="62">
+        <f t="shared" si="5"/>
         <v>654</v>
       </c>
-      <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B110, $C$2:$C$692, C110, $D$2:$D$692, D110, $E$2:$E$692, E110) &gt; 1, "Duplicate", "Unique")</f>
+      <c r="N110" s="63" t="str">
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6478,11 +6496,11 @@
         <v>33950</v>
       </c>
       <c r="M111" s="18">
-        <f>ABS((D111*E111)-L111)</f>
+        <f t="shared" si="5"/>
         <v>850</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B111, $C$2:$C$692, C111, $D$2:$D$692, D111, $E$2:$E$692, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6524,11 +6542,11 @@
         <v>10300</v>
       </c>
       <c r="M112" s="18">
-        <f>ABS((D112*E112)-L112)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B112, $C$2:$C$692, C112, $D$2:$D$692, D112, $E$2:$E$692, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P112" s="29"/>
@@ -6571,11 +6589,11 @@
         <v>20260</v>
       </c>
       <c r="M113" s="18">
-        <f>ABS((D113*E113)-L113)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N113" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B113, $C$2:$C$692, C113, $D$2:$D$692, D113, $E$2:$E$692, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O113"/>
@@ -6619,11 +6637,11 @@
         <v>17150</v>
       </c>
       <c r="M114" s="18">
-        <f>ABS((D114*E114)-L114)</f>
+        <f t="shared" si="5"/>
         <v>300</v>
       </c>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B114, $C$2:$C$692, C114, $D$2:$D$692, D114, $E$2:$E$692, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6657,7 +6675,7 @@
       </c>
       <c r="J115" s="34"/>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B115, $C$2:$C$692, C115, $D$2:$D$692, D115, $E$2:$E$692, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6704,7 +6722,7 @@
         <v>300</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B116, $C$2:$C$692, C116, $D$2:$D$692, D116, $E$2:$E$692, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6750,7 +6768,7 @@
         <v>710.99999999999636</v>
       </c>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B117, $C$2:$C$692, C117, $D$2:$D$692, D117, $E$2:$E$692, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P117"/>
@@ -6790,7 +6808,7 @@
       <c r="L118" s="18"/>
       <c r="M118" s="18"/>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B118, $C$2:$C$692, C118, $D$2:$D$692, D118, $E$2:$E$692, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="10"/>
@@ -6826,7 +6844,7 @@
       </c>
       <c r="J119" s="34"/>
       <c r="N119" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B119, $C$2:$C$692, C119, $D$2:$D$692, D119, $E$2:$E$692, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6860,7 +6878,7 @@
       </c>
       <c r="J120" s="34"/>
       <c r="N120" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B120, $C$2:$C$692, C120, $D$2:$D$692, D120, $E$2:$E$692, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -6892,7 +6910,7 @@
       <c r="I121" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J121" s="56" t="s">
+      <c r="J121" s="54" t="s">
         <v>118</v>
       </c>
       <c r="K121" s="27" t="s">
@@ -6906,7 +6924,7 @@
         <v>527.5</v>
       </c>
       <c r="N121" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B121, $C$2:$C$692, C121, $D$2:$D$692, D121, $E$2:$E$692, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="29"/>
@@ -6949,7 +6967,7 @@
       <c r="L122" s="27"/>
       <c r="M122" s="27"/>
       <c r="N122" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B122, $C$2:$C$692, C122, $D$2:$D$692, D122, $E$2:$E$692, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O122" s="29"/>
@@ -6983,18 +7001,20 @@
       <c r="I123" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J123" s="34"/>
+      <c r="J123" s="34" t="s">
+        <v>117</v>
+      </c>
       <c r="K123" s="18"/>
       <c r="L123" s="18"/>
       <c r="M123" s="18"/>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B123, $C$2:$C$692, C123, $D$2:$D$692, D123, $E$2:$E$692, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="10"/>
       <c r="P123" s="10"/>
     </row>
-    <row r="124" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A124" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -7036,7 +7056,7 @@
         <v>880</v>
       </c>
       <c r="N124" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B124, $C$2:$C$692, C124, $D$2:$D$692, D124, $E$2:$E$692, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124" s="38" t="s">
@@ -7085,7 +7105,7 @@
         <v>500</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B125, $C$2:$C$692, C125, $D$2:$D$692, D125, $E$2:$E$692, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7131,7 +7151,7 @@
         <v>300</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B126, $C$2:$C$692, C126, $D$2:$D$692, D126, $E$2:$E$692, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O126" s="29"/>
@@ -7178,7 +7198,7 @@
         <v>660</v>
       </c>
       <c r="N127" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B127, $C$2:$C$692, C127, $D$2:$D$692, D127, $E$2:$E$692, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O127" s="24"/>
@@ -7228,7 +7248,7 @@
         <v>300</v>
       </c>
       <c r="N128" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B128, $C$2:$C$692, C128, $D$2:$D$692, D128, $E$2:$E$692, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -7266,7 +7286,7 @@
         <v>194</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B129, $C$2:$C$692, C129, $D$2:$D$692, D129, $E$2:$E$692, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7312,7 +7332,7 @@
         <v>320</v>
       </c>
       <c r="N130" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B130, $C$2:$C$692, C130, $D$2:$D$692, D130, $E$2:$E$692, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="6">IF(COUNTIFS( $B$2:$B$692, B130, $C$2:$C$692, C130, $D$2:$D$692, D130, $E$2:$E$692, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O130" s="29"/>
@@ -7360,7 +7380,7 @@
         <v>235</v>
       </c>
       <c r="N131" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B131, $C$2:$C$692, C131, $D$2:$D$692, D131, $E$2:$E$692, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7392,14 +7412,14 @@
       <c r="I132" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J132" s="54" t="s">
+      <c r="J132" s="51" t="s">
         <v>55</v>
       </c>
       <c r="K132" s="17"/>
       <c r="L132" s="17"/>
       <c r="M132" s="17"/>
       <c r="N132" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B132, $C$2:$C$692, C132, $D$2:$D$692, D132, $E$2:$E$692, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7438,11 +7458,11 @@
         <v>144</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B133, $C$2:$C$692, C133, $D$2:$D$692, D133, $E$2:$E$692, E133) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="134" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A134" s="3">
         <v>46281.375</v>
       </c>
@@ -7484,14 +7504,14 @@
         <v>1400</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B134, $C$2:$C$692, C134, $D$2:$D$692, D134, $E$2:$E$692, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="38" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="135" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A135" s="11">
         <v>46273.375</v>
       </c>
@@ -7533,7 +7553,7 @@
         <v>200</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B135, $C$2:$C$692, C135, $D$2:$D$692, D135, $E$2:$E$692, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O135" s="38" t="s">
@@ -7582,13 +7602,13 @@
         <v>650</v>
       </c>
       <c r="N136" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B136, $C$2:$C$692, C136, $D$2:$D$692, D136, $E$2:$E$692, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O136" s="10"/>
       <c r="P136" s="10"/>
     </row>
-    <row r="137" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A137" s="3">
         <v>46261.615277777775</v>
       </c>
@@ -7630,7 +7650,7 @@
         <v>501</v>
       </c>
       <c r="N137" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B137, $C$2:$C$692, C137, $D$2:$D$692, D137, $E$2:$E$692, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O137" s="38" t="s">
@@ -7668,7 +7688,7 @@
       </c>
       <c r="J138" s="34"/>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B138, $C$2:$C$692, C138, $D$2:$D$692, D138, $E$2:$E$692, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="24"/>
@@ -7715,7 +7735,7 @@
         <v>500</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B139, $C$2:$C$692, C139, $D$2:$D$692, D139, $E$2:$E$692, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7761,7 +7781,7 @@
         <v>300</v>
       </c>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B140, $C$2:$C$692, C140, $D$2:$D$692, D140, $E$2:$E$692, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7795,7 +7815,7 @@
       </c>
       <c r="J141" s="34"/>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B141, $C$2:$C$692, C141, $D$2:$D$692, D141, $E$2:$E$692, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7837,11 +7857,11 @@
         <v>4852</v>
       </c>
       <c r="M142" s="18">
-        <f>ABS((D142*E142)-L142)</f>
+        <f t="shared" ref="M142:M147" si="7">ABS((D142*E142)-L142)</f>
         <v>300</v>
       </c>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B142, $C$2:$C$692, C142, $D$2:$D$692, D142, $E$2:$E$692, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -7883,15 +7903,15 @@
         <v>10510</v>
       </c>
       <c r="M143" s="18">
-        <f>ABS((D143*E143)-L143)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N143" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B143, $C$2:$C$692, C143, $D$2:$D$692, D143, $E$2:$E$692, E143) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="144" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A144" s="30">
         <v>46281.443055555559</v>
       </c>
@@ -7929,11 +7949,11 @@
         <v>5585</v>
       </c>
       <c r="M144" s="27">
-        <f>ABS((D144*E144)-L144)</f>
+        <f t="shared" si="7"/>
         <v>395</v>
       </c>
       <c r="N144" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B144, $C$2:$C$692, C144, $D$2:$D$692, D144, $E$2:$E$692, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O144" s="38" t="s">
@@ -7941,7 +7961,7 @@
       </c>
       <c r="P144" s="29"/>
     </row>
-    <row r="145" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A145" s="30">
         <v>46281.388888888891</v>
       </c>
@@ -7979,11 +7999,11 @@
         <v>5730</v>
       </c>
       <c r="M145" s="27">
-        <f>ABS((D145*E145)-L145)</f>
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
       <c r="N145" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B145, $C$2:$C$692, C145, $D$2:$D$692, D145, $E$2:$E$692, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O145" s="38" t="s">
@@ -8029,11 +8049,11 @@
         <v>3810</v>
       </c>
       <c r="M146" s="18">
-        <f>ABS((D146*E146)-L146)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N146" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B146, $C$2:$C$692, C146, $D$2:$D$692, D146, $E$2:$E$692, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8075,17 +8095,17 @@
         <v>14440</v>
       </c>
       <c r="M147" s="18">
-        <f>ABS((D147*E147)-L147)</f>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N147" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B147, $C$2:$C$692, C147, $D$2:$D$692, D147, $E$2:$E$692, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O147"/>
       <c r="P147" s="10"/>
     </row>
-    <row r="148" spans="1:16" s="29" customFormat="1" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:16" s="29" customFormat="1" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A148" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8120,7 +8140,7 @@
       <c r="L148" s="18"/>
       <c r="M148" s="18"/>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B148, $C$2:$C$692, C148, $D$2:$D$692, D148, $E$2:$E$692, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="38" t="s">
@@ -8170,7 +8190,7 @@
         <v>650</v>
       </c>
       <c r="N149" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B149, $C$2:$C$692, C149, $D$2:$D$692, D149, $E$2:$E$692, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="29"/>
@@ -8218,7 +8238,7 @@
         <v>934</v>
       </c>
       <c r="N150" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B150, $C$2:$C$692, C150, $D$2:$D$692, D150, $E$2:$E$692, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O150" s="29"/>
@@ -8266,7 +8286,7 @@
         <v>300</v>
       </c>
       <c r="N151" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B151, $C$2:$C$692, C151, $D$2:$D$692, D151, $E$2:$E$692, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8312,7 +8332,7 @@
         <v>376</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B152, $C$2:$C$692, C152, $D$2:$D$692, D152, $E$2:$E$692, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8348,7 +8368,7 @@
         <v>118</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B153, $C$2:$C$692, C153, $D$2:$D$692, D153, $E$2:$E$692, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P153"/>
@@ -8383,7 +8403,7 @@
       </c>
       <c r="J154" s="34"/>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B154, $C$2:$C$692, C154, $D$2:$D$692, D154, $E$2:$E$692, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O154" s="29"/>
@@ -8430,11 +8450,11 @@
         <v>810</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B155, $C$2:$C$692, C155, $D$2:$D$692, D155, $E$2:$E$692, E155) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A156" s="3">
         <v>46266.375</v>
       </c>
@@ -8476,7 +8496,7 @@
         <v>300</v>
       </c>
       <c r="N156" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B156, $C$2:$C$692, C156, $D$2:$D$692, D156, $E$2:$E$692, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O156" s="38" t="s">
@@ -8516,7 +8536,7 @@
         <v>118</v>
       </c>
       <c r="N157" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B157, $C$2:$C$692, C157, $D$2:$D$692, D157, $E$2:$E$692, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8562,7 +8582,7 @@
         <v>1700</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B158, $C$2:$C$692, C158, $D$2:$D$692, D158, $E$2:$E$692, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O158" s="29"/>
@@ -8595,14 +8615,14 @@
       <c r="I159" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J159" s="54" t="s">
+      <c r="J159" s="51" t="s">
         <v>41</v>
       </c>
       <c r="K159" s="17"/>
       <c r="L159" s="17"/>
       <c r="M159" s="17"/>
       <c r="N159" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B159, $C$2:$C$692, C159, $D$2:$D$692, D159, $E$2:$E$692, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O159" s="10"/>
@@ -8650,7 +8670,7 @@
         <v>420</v>
       </c>
       <c r="N160" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B160, $C$2:$C$692, C160, $D$2:$D$692, D160, $E$2:$E$692, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8696,7 +8716,7 @@
         <v>275</v>
       </c>
       <c r="N161" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B161, $C$2:$C$692, C161, $D$2:$D$692, D161, $E$2:$E$692, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8742,7 +8762,7 @@
         <v>225</v>
       </c>
       <c r="N162" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B162, $C$2:$C$692, C162, $D$2:$D$692, D162, $E$2:$E$692, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -8778,7 +8798,7 @@
         <v>118</v>
       </c>
       <c r="N163" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B163, $C$2:$C$692, C163, $D$2:$D$692, D163, $E$2:$E$692, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8824,7 +8844,7 @@
         <v>300</v>
       </c>
       <c r="N164" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B164, $C$2:$C$692, C164, $D$2:$D$692, D164, $E$2:$E$692, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8870,7 +8890,7 @@
         <v>188</v>
       </c>
       <c r="N165" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B165, $C$2:$C$692, C165, $D$2:$D$692, D165, $E$2:$E$692, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O165" s="29"/>
@@ -8906,7 +8926,7 @@
       </c>
       <c r="J166" s="34"/>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B166, $C$2:$C$692, C166, $D$2:$D$692, D166, $E$2:$E$692, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P166" s="29"/>
@@ -8953,7 +8973,7 @@
         <v>500</v>
       </c>
       <c r="N167" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B167, $C$2:$C$692, C167, $D$2:$D$692, D167, $E$2:$E$692, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -8989,7 +9009,7 @@
         <v>117</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B168, $C$2:$C$692, C168, $D$2:$D$692, D168, $E$2:$E$692, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9028,7 +9048,7 @@
       <c r="L169" s="44"/>
       <c r="M169" s="44"/>
       <c r="N169" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B169, $C$2:$C$692, C169, $D$2:$D$692, D169, $E$2:$E$692, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="24"/>
@@ -9078,7 +9098,7 @@
         <v>300</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B170, $C$2:$C$692, C170, $D$2:$D$692, D170, $E$2:$E$692, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P170" s="19"/>
@@ -9113,7 +9133,7 @@
       </c>
       <c r="J171" s="34"/>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B171, $C$2:$C$692, C171, $D$2:$D$692, D171, $E$2:$E$692, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9147,7 +9167,7 @@
       </c>
       <c r="J172" s="34"/>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B172, $C$2:$C$692, C172, $D$2:$D$692, D172, $E$2:$E$692, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9193,7 +9213,7 @@
         <v>294</v>
       </c>
       <c r="N173" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B173, $C$2:$C$692, C173, $D$2:$D$692, D173, $E$2:$E$692, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -9239,7 +9259,7 @@
         <v>294</v>
       </c>
       <c r="N174" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B174, $C$2:$C$692, C174, $D$2:$D$692, D174, $E$2:$E$692, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -9285,13 +9305,13 @@
         <v>280</v>
       </c>
       <c r="N175" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B175, $C$2:$C$692, C175, $D$2:$D$692, D175, $E$2:$E$692, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O175" s="29"/>
       <c r="P175" s="29"/>
     </row>
-    <row r="176" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A176" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -9333,7 +9353,7 @@
         <v>500</v>
       </c>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B176, $C$2:$C$692, C176, $D$2:$D$692, D176, $E$2:$E$692, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O176" s="39" t="s">
@@ -9382,7 +9402,7 @@
         <v>1000</v>
       </c>
       <c r="N177" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B177, $C$2:$C$692, C177, $D$2:$D$692, D177, $E$2:$E$692, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="P177" s="29"/>
@@ -9419,7 +9439,7 @@
         <v>55</v>
       </c>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B178, $C$2:$C$692, C178, $D$2:$D$692, D178, $E$2:$E$692, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9455,7 +9475,7 @@
         <v>117</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B179, $C$2:$C$692, C179, $D$2:$D$692, D179, $E$2:$E$692, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9491,7 +9511,7 @@
         <v>117</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B180, $C$2:$C$692, C180, $D$2:$D$692, D180, $E$2:$E$692, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9533,11 +9553,11 @@
         <v>2105</v>
       </c>
       <c r="M181" s="26">
-        <f>ABS((D181*E181)-L181)</f>
+        <f t="shared" ref="M181:M186" si="8">ABS((D181*E181)-L181)</f>
         <v>250</v>
       </c>
       <c r="N181" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B181, $C$2:$C$692, C181, $D$2:$D$692, D181, $E$2:$E$692, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9579,11 +9599,11 @@
         <v>4680</v>
       </c>
       <c r="M182" s="27">
-        <f>ABS((D182*E182)-L182)</f>
+        <f t="shared" si="8"/>
         <v>140</v>
       </c>
       <c r="N182" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B182, $C$2:$C$692, C182, $D$2:$D$692, D182, $E$2:$E$692, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="P182" s="29"/>
@@ -9626,11 +9646,11 @@
         <v>4520</v>
       </c>
       <c r="M183" s="27">
-        <f>ABS((D183*E183)-L183)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N183" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B183, $C$2:$C$692, C183, $D$2:$D$692, D183, $E$2:$E$692, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Duplicate</v>
       </c>
       <c r="O183" s="10"/>
@@ -9674,11 +9694,11 @@
         <v>14650</v>
       </c>
       <c r="M184" s="18">
-        <f>ABS((D184*E184)-L184)</f>
+        <f t="shared" si="8"/>
         <v>450</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B184, $C$2:$C$692, C184, $D$2:$D$692, D184, $E$2:$E$692, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9720,11 +9740,11 @@
         <v>12510</v>
       </c>
       <c r="M185" s="18">
-        <f>ABS((D185*E185)-L185)</f>
+        <f t="shared" si="8"/>
         <v>290</v>
       </c>
       <c r="N185" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B185, $C$2:$C$692, C185, $D$2:$D$692, D185, $E$2:$E$692, E185) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9766,11 +9786,11 @@
         <v>3180</v>
       </c>
       <c r="M186" s="18">
-        <f>ABS((D186*E186)-L186)</f>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="N186" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B186, $C$2:$C$692, C186, $D$2:$D$692, D186, $E$2:$E$692, E186) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9806,7 +9826,7 @@
         <v>118</v>
       </c>
       <c r="N187" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B187, $C$2:$C$692, C187, $D$2:$D$692, D187, $E$2:$E$692, E187) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9852,7 +9872,7 @@
         <v>300</v>
       </c>
       <c r="N188" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B188, $C$2:$C$692, C188, $D$2:$D$692, D188, $E$2:$E$692, E188) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9886,7 +9906,7 @@
       </c>
       <c r="J189" s="34"/>
       <c r="N189" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B189, $C$2:$C$692, C189, $D$2:$D$692, D189, $E$2:$E$692, E189) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -9932,11 +9952,11 @@
         <v>940</v>
       </c>
       <c r="N190" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B190, $C$2:$C$692, C190, $D$2:$D$692, D190, $E$2:$E$692, E190) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="191" spans="1:16" ht="39" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="6"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16" ht="39" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A191" s="3">
         <v>46274.414583333331</v>
       </c>
@@ -9978,7 +9998,7 @@
         <v>646</v>
       </c>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B191, $C$2:$C$692, C191, $D$2:$D$692, D191, $E$2:$E$692, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O191" s="38" t="s">
@@ -10027,7 +10047,7 @@
         <v>300</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B192, $C$2:$C$692, C192, $D$2:$D$692, D192, $E$2:$E$692, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="10"/>
@@ -10065,7 +10085,7 @@
         <v>118</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B193, $C$2:$C$692, C193, $D$2:$D$692, D193, $E$2:$E$692, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="6"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10111,7 +10131,7 @@
         <v>800</v>
       </c>
       <c r="N194" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B194, $C$2:$C$692, C194, $D$2:$D$692, D194, $E$2:$E$692, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="9">IF(COUNTIFS( $B$2:$B$692, B194, $C$2:$C$692, C194, $D$2:$D$692, D194, $E$2:$E$692, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -10157,7 +10177,7 @@
         <v>275</v>
       </c>
       <c r="N195" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B195, $C$2:$C$692, C195, $D$2:$D$692, D195, $E$2:$E$692, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10193,7 +10213,7 @@
         <v>55</v>
       </c>
       <c r="N196" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B196, $C$2:$C$692, C196, $D$2:$D$692, D196, $E$2:$E$692, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10239,7 +10259,7 @@
         <v>300</v>
       </c>
       <c r="N197" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B197, $C$2:$C$692, C197, $D$2:$D$692, D197, $E$2:$E$692, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10273,7 +10293,7 @@
       </c>
       <c r="J198" s="34"/>
       <c r="N198" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B198, $C$2:$C$692, C198, $D$2:$D$692, D198, $E$2:$E$692, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10309,7 +10329,7 @@
         <v>118</v>
       </c>
       <c r="N199" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B199, $C$2:$C$692, C199, $D$2:$D$692, D199, $E$2:$E$692, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="29"/>
@@ -10356,11 +10376,11 @@
         <v>360</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B200, $C$2:$C$692, C200, $D$2:$D$692, D200, $E$2:$E$692, E200) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="201" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="201" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A201" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -10402,7 +10422,7 @@
         <v>48320</v>
       </c>
       <c r="N201" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B201, $C$2:$C$692, C201, $D$2:$D$692, D201, $E$2:$E$692, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O201" s="38" t="s">
@@ -10439,7 +10459,7 @@
       </c>
       <c r="J202" s="34"/>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B202, $C$2:$C$692, C202, $D$2:$D$692, D202, $E$2:$E$692, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10475,7 +10495,7 @@
         <v>118</v>
       </c>
       <c r="N203" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B203, $C$2:$C$692, C203, $D$2:$D$692, D203, $E$2:$E$692, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10521,7 +10541,7 @@
         <v>650</v>
       </c>
       <c r="N204" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B204, $C$2:$C$692, C204, $D$2:$D$692, D204, $E$2:$E$692, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O204" s="29"/>
@@ -10568,7 +10588,7 @@
         <v>260</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B205, $C$2:$C$692, C205, $D$2:$D$692, D205, $E$2:$E$692, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10614,7 +10634,7 @@
         <v>816</v>
       </c>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B206, $C$2:$C$692, C206, $D$2:$D$692, D206, $E$2:$E$692, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10648,11 +10668,11 @@
       </c>
       <c r="J207" s="34"/>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B207, $C$2:$C$692, C207, $D$2:$D$692, D207, $E$2:$E$692, E207) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="208" spans="1:15" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="208" spans="1:15" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A208" s="3">
         <v>46335.421527777777</v>
       </c>
@@ -10694,7 +10714,7 @@
         <v>800</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B208, $C$2:$C$692, C208, $D$2:$D$692, D208, $E$2:$E$692, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O208" s="38" t="s">
@@ -10743,7 +10763,7 @@
         <v>150</v>
       </c>
       <c r="N209" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B209, $C$2:$C$692, C209, $D$2:$D$692, D209, $E$2:$E$692, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -10789,7 +10809,7 @@
         <v>250</v>
       </c>
       <c r="N210" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B210, $C$2:$C$692, C210, $D$2:$D$692, D210, $E$2:$E$692, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -10823,7 +10843,7 @@
       </c>
       <c r="J211" s="34"/>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B211, $C$2:$C$692, C211, $D$2:$D$692, D211, $E$2:$E$692, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10862,7 +10882,7 @@
         <v>145</v>
       </c>
       <c r="N212" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B212, $C$2:$C$692, C212, $D$2:$D$692, D212, $E$2:$E$692, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10908,7 +10928,7 @@
         <v>480</v>
       </c>
       <c r="N213" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B213, $C$2:$C$692, C213, $D$2:$D$692, D213, $E$2:$E$692, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10942,7 +10962,7 @@
       </c>
       <c r="J214" s="34"/>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B214, $C$2:$C$692, C214, $D$2:$D$692, D214, $E$2:$E$692, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -10978,7 +10998,7 @@
         <v>118</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B215, $C$2:$C$692, C215, $D$2:$D$692, D215, $E$2:$E$692, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O215" s="29"/>
@@ -11013,7 +11033,7 @@
       </c>
       <c r="J216" s="34"/>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B216, $C$2:$C$692, C216, $D$2:$D$692, D216, $E$2:$E$692, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11059,7 +11079,7 @@
         <v>650</v>
       </c>
       <c r="N217" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B217, $C$2:$C$692, C217, $D$2:$D$692, D217, $E$2:$E$692, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P217" s="29"/>
@@ -11106,7 +11126,7 @@
         <v>450</v>
       </c>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B218, $C$2:$C$692, C218, $D$2:$D$692, D218, $E$2:$E$692, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11152,7 +11172,7 @@
         <v>250</v>
       </c>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B219, $C$2:$C$692, C219, $D$2:$D$692, D219, $E$2:$E$692, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11198,7 +11218,7 @@
         <v>300</v>
       </c>
       <c r="N220" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B220, $C$2:$C$692, C220, $D$2:$D$692, D220, $E$2:$E$692, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11234,7 +11254,7 @@
         <v>117</v>
       </c>
       <c r="N221" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B221, $C$2:$C$692, C221, $D$2:$D$692, D221, $E$2:$E$692, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11270,7 +11290,7 @@
         <v>118</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B222, $C$2:$C$692, C222, $D$2:$D$692, D222, $E$2:$E$692, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11306,7 +11326,7 @@
         <v>117</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B223, $C$2:$C$692, C223, $D$2:$D$692, D223, $E$2:$E$692, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11352,7 +11372,7 @@
         <v>651</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B224, $C$2:$C$692, C224, $D$2:$D$692, D224, $E$2:$E$692, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11388,7 +11408,7 @@
         <v>117</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B225, $C$2:$C$692, C225, $D$2:$D$692, D225, $E$2:$E$692, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11434,12 +11454,12 @@
         <v>650</v>
       </c>
       <c r="N226" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B226, $C$2:$C$692, C226, $D$2:$D$692, D226, $E$2:$E$692, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P226" s="29"/>
     </row>
-    <row r="227" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A227" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -11481,7 +11501,7 @@
         <v>47900</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B227, $C$2:$C$692, C227, $D$2:$D$692, D227, $E$2:$E$692, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="38" t="s">
@@ -11530,7 +11550,7 @@
         <v>400</v>
       </c>
       <c r="N228" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B228, $C$2:$C$692, C228, $D$2:$D$692, D228, $E$2:$E$692, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11566,7 +11586,7 @@
         <v>117</v>
       </c>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B229, $C$2:$C$692, C229, $D$2:$D$692, D229, $E$2:$E$692, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11603,7 +11623,7 @@
       <c r="L230" s="18"/>
       <c r="M230" s="18"/>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B230, $C$2:$C$692, C230, $D$2:$D$692, D230, $E$2:$E$692, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O230" s="10"/>
@@ -11642,13 +11662,13 @@
       <c r="L231" s="18"/>
       <c r="M231" s="18"/>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B231, $C$2:$C$692, C231, $D$2:$D$692, D231, $E$2:$E$692, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O231" s="10"/>
       <c r="P231" s="10"/>
     </row>
-    <row r="232" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A232" s="3">
         <v>46266.375</v>
       </c>
@@ -11690,14 +11710,14 @@
         <v>650</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B232, $C$2:$C$692, C232, $D$2:$D$692, D232, $E$2:$E$692, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O232" s="38" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="233" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A233" s="3">
         <v>46267.513888888891</v>
       </c>
@@ -11739,7 +11759,7 @@
         <v>495</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B233, $C$2:$C$692, C233, $D$2:$D$692, D233, $E$2:$E$692, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O233" s="38" t="s">
@@ -11776,11 +11796,11 @@
       </c>
       <c r="J234" s="34"/>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B234, $C$2:$C$692, C234, $D$2:$D$692, D234, $E$2:$E$692, E234) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+        <f t="shared" si="9"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A235" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -11822,7 +11842,7 @@
         <v>300</v>
       </c>
       <c r="N235" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B235, $C$2:$C$692, C235, $D$2:$D$692, D235, $E$2:$E$692, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O235" s="38" t="s">
@@ -11872,7 +11892,7 @@
         <v>320</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B236, $C$2:$C$692, C236, $D$2:$D$692, D236, $E$2:$E$692, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11918,7 +11938,7 @@
         <v>448</v>
       </c>
       <c r="N237" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B237, $C$2:$C$692, C237, $D$2:$D$692, D237, $E$2:$E$692, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11954,7 +11974,7 @@
         <v>117</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B238, $C$2:$C$692, C238, $D$2:$D$692, D238, $E$2:$E$692, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -11990,7 +12010,7 @@
         <v>118</v>
       </c>
       <c r="N239" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B239, $C$2:$C$692, C239, $D$2:$D$692, D239, $E$2:$E$692, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O239" s="29"/>
@@ -12037,7 +12057,7 @@
         <v>250</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B240, $C$2:$C$692, C240, $D$2:$D$692, D240, $E$2:$E$692, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P240" s="29"/>
@@ -12084,7 +12104,7 @@
         <v>268</v>
       </c>
       <c r="N241" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B241, $C$2:$C$692, C241, $D$2:$D$692, D241, $E$2:$E$692, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12130,7 +12150,7 @@
         <v>650</v>
       </c>
       <c r="N242" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B242, $C$2:$C$692, C242, $D$2:$D$692, D242, $E$2:$E$692, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O242"/>
@@ -12178,7 +12198,7 @@
         <v>300</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B243, $C$2:$C$692, C243, $D$2:$D$692, D243, $E$2:$E$692, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="10"/>
@@ -12216,7 +12236,7 @@
         <v>117</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B244, $C$2:$C$692, C244, $D$2:$D$692, D244, $E$2:$E$692, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12252,7 +12272,7 @@
         <v>118</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B245, $C$2:$C$692, C245, $D$2:$D$692, D245, $E$2:$E$692, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12286,7 +12306,7 @@
       </c>
       <c r="J246" s="34"/>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B246, $C$2:$C$692, C246, $D$2:$D$692, D246, $E$2:$E$692, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12325,7 +12345,7 @@
       <c r="L247" s="18"/>
       <c r="M247" s="18"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B247, $C$2:$C$692, C247, $D$2:$D$692, D247, $E$2:$E$692, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="10"/>
@@ -12363,7 +12383,7 @@
         <v>117</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B248, $C$2:$C$692, C248, $D$2:$D$692, D248, $E$2:$E$692, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12409,7 +12429,7 @@
         <v>370</v>
       </c>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B249, $C$2:$C$692, C249, $D$2:$D$692, D249, $E$2:$E$692, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P249" s="29"/>
@@ -12456,7 +12476,7 @@
         <v>47480</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B250, $C$2:$C$692, C250, $D$2:$D$692, D250, $E$2:$E$692, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12492,7 +12512,7 @@
         <v>117</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B251, $C$2:$C$692, C251, $D$2:$D$692, D251, $E$2:$E$692, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12538,7 +12558,7 @@
         <v>340</v>
       </c>
       <c r="N252" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B252, $C$2:$C$692, C252, $D$2:$D$692, D252, $E$2:$E$692, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="10"/>
@@ -12586,7 +12606,7 @@
         <v>300</v>
       </c>
       <c r="N253" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B253, $C$2:$C$692, C253, $D$2:$D$692, D253, $E$2:$E$692, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O253" s="10"/>
@@ -12624,7 +12644,7 @@
         <v>117</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B254, $C$2:$C$692, C254, $D$2:$D$692, D254, $E$2:$E$692, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P254" s="29"/>
@@ -12659,7 +12679,7 @@
       </c>
       <c r="J255" s="34"/>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B255, $C$2:$C$692, C255, $D$2:$D$692, D255, $E$2:$E$692, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12705,7 +12725,7 @@
         <v>300</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B256, $C$2:$C$692, C256, $D$2:$D$692, D256, $E$2:$E$692, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="10"/>
@@ -12743,7 +12763,7 @@
         <v>118</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B257, $C$2:$C$692, C257, $D$2:$D$692, D257, $E$2:$E$692, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12777,7 +12797,7 @@
       </c>
       <c r="J258" s="34"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B258, $C$2:$C$692, C258, $D$2:$D$692, D258, $E$2:$E$692, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N298" si="10">IF(COUNTIFS( $B$2:$B$692, B258, $C$2:$C$692, C258, $D$2:$D$692, D258, $E$2:$E$692, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -12823,7 +12843,7 @@
         <v>235</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B259, $C$2:$C$692, C259, $D$2:$D$692, D259, $E$2:$E$692, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O259" s="10"/>
@@ -12871,7 +12891,7 @@
         <v>300</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B260, $C$2:$C$692, C260, $D$2:$D$692, D260, $E$2:$E$692, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="10"/>
@@ -12909,7 +12929,7 @@
         <v>118</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B261, $C$2:$C$692, C261, $D$2:$D$692, D261, $E$2:$E$692, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12955,7 +12975,7 @@
         <v>250</v>
       </c>
       <c r="N262" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B262, $C$2:$C$692, C262, $D$2:$D$692, D262, $E$2:$E$692, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12991,7 +13011,7 @@
         <v>118</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B263, $C$2:$C$692, C263, $D$2:$D$692, D263, $E$2:$E$692, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13025,7 +13045,7 @@
       </c>
       <c r="J264" s="34"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B264, $C$2:$C$692, C264, $D$2:$D$692, D264, $E$2:$E$692, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="29"/>
@@ -13072,7 +13092,7 @@
         <v>1800</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B265, $C$2:$C$692, C265, $D$2:$D$692, D265, $E$2:$E$692, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13106,12 +13126,12 @@
       </c>
       <c r="J266" s="34"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B266, $C$2:$C$692, C266, $D$2:$D$692, D266, $E$2:$E$692, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O266" s="29"/>
     </row>
-    <row r="267" spans="1:16" ht="26.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:16" ht="26.5" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A267" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -13153,7 +13173,7 @@
         <v>500</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B267, $C$2:$C$692, C267, $D$2:$D$692, D267, $E$2:$E$692, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O267" s="38" t="s">
@@ -13202,7 +13222,7 @@
         <v>300</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B268, $C$2:$C$692, C268, $D$2:$D$692, D268, $E$2:$E$692, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13243,7 +13263,7 @@
       <c r="L269" s="17"/>
       <c r="M269" s="17"/>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B269, $C$2:$C$692, C269, $D$2:$D$692, D269, $E$2:$E$692, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13289,7 +13309,7 @@
         <v>260</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B270, $C$2:$C$692, C270, $D$2:$D$692, D270, $E$2:$E$692, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13325,7 +13345,7 @@
         <v>117</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B271, $C$2:$C$692, C271, $D$2:$D$692, D271, $E$2:$E$692, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13361,7 +13381,7 @@
         <v>118</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B272, $C$2:$C$692, C272, $D$2:$D$692, D272, $E$2:$E$692, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13397,7 +13417,7 @@
         <v>153</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B273, $C$2:$C$692, C273, $D$2:$D$692, D273, $E$2:$E$692, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13433,7 +13453,7 @@
         <v>118</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B274, $C$2:$C$692, C274, $D$2:$D$692, D274, $E$2:$E$692, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13469,7 +13489,7 @@
         <v>117</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B275, $C$2:$C$692, C275, $D$2:$D$692, D275, $E$2:$E$692, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13515,7 +13535,7 @@
         <v>250</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B276, $C$2:$C$692, C276, $D$2:$D$692, D276, $E$2:$E$692, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O276" s="10"/>
@@ -13563,7 +13583,7 @@
         <v>300</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B277, $C$2:$C$692, C277, $D$2:$D$692, D277, $E$2:$E$692, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O277" s="10"/>
@@ -13599,7 +13619,7 @@
       </c>
       <c r="J278" s="34"/>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B278, $C$2:$C$692, C278, $D$2:$D$692, D278, $E$2:$E$692, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P278" s="29"/>
@@ -13646,7 +13666,7 @@
         <v>285</v>
       </c>
       <c r="N279" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B279, $C$2:$C$692, C279, $D$2:$D$692, D279, $E$2:$E$692, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13692,7 +13712,7 @@
         <v>726</v>
       </c>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B280, $C$2:$C$692, C280, $D$2:$D$692, D280, $E$2:$E$692, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13726,7 +13746,7 @@
       </c>
       <c r="J281" s="34"/>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B281, $C$2:$C$692, C281, $D$2:$D$692, D281, $E$2:$E$692, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13760,7 +13780,7 @@
       </c>
       <c r="J282" s="34"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B282, $C$2:$C$692, C282, $D$2:$D$692, D282, $E$2:$E$692, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13794,7 +13814,7 @@
       </c>
       <c r="J283" s="34"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B283, $C$2:$C$692, C283, $D$2:$D$692, D283, $E$2:$E$692, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P283" s="29"/>
@@ -13841,7 +13861,7 @@
         <v>275</v>
       </c>
       <c r="N284" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B284, $C$2:$C$692, C284, $D$2:$D$692, D284, $E$2:$E$692, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13887,7 +13907,7 @@
         <v>250</v>
       </c>
       <c r="N285" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B285, $C$2:$C$692, C285, $D$2:$D$692, D285, $E$2:$E$692, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P285" s="29"/>
@@ -13922,7 +13942,7 @@
       </c>
       <c r="J286" s="34"/>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B286, $C$2:$C$692, C286, $D$2:$D$692, D286, $E$2:$E$692, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13956,7 +13976,7 @@
       </c>
       <c r="J287" s="34"/>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B287, $C$2:$C$692, C287, $D$2:$D$692, D287, $E$2:$E$692, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14002,7 +14022,7 @@
         <v>300</v>
       </c>
       <c r="N288" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B288, $C$2:$C$692, C288, $D$2:$D$692, D288, $E$2:$E$692, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14038,7 +14058,7 @@
         <v>118</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B289, $C$2:$C$692, C289, $D$2:$D$692, D289, $E$2:$E$692, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14072,7 +14092,7 @@
       </c>
       <c r="J290" s="34"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B290, $C$2:$C$692, C290, $D$2:$D$692, D290, $E$2:$E$692, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14108,7 +14128,7 @@
         <v>55</v>
       </c>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B291, $C$2:$C$692, C291, $D$2:$D$692, D291, $E$2:$E$692, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14144,7 +14164,7 @@
         <v>118</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B292, $C$2:$C$692, C292, $D$2:$D$692, D292, $E$2:$E$692, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14180,7 +14200,7 @@
         <v>118</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B293, $C$2:$C$692, C293, $D$2:$D$692, D293, $E$2:$E$692, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14214,7 +14234,7 @@
       </c>
       <c r="J294" s="34"/>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B294, $C$2:$C$692, C294, $D$2:$D$692, D294, $E$2:$E$692, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14260,7 +14280,7 @@
         <v>250</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B295, $C$2:$C$692, C295, $D$2:$D$692, D295, $E$2:$E$692, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -14299,7 +14319,7 @@
       <c r="L296" s="27"/>
       <c r="M296" s="27"/>
       <c r="N296" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B296, $C$2:$C$692, C296, $D$2:$D$692, D296, $E$2:$E$692, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O296" s="29"/>
@@ -14340,7 +14360,7 @@
       <c r="L297" s="27"/>
       <c r="M297" s="27"/>
       <c r="N297" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B297, $C$2:$C$692, C297, $D$2:$D$692, D297, $E$2:$E$692, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O297" s="29"/>
@@ -14378,7 +14398,7 @@
         <v>117</v>
       </c>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B298, $C$2:$C$692, C298, $D$2:$D$692, D298, $E$2:$E$692, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -21923,6 +21943,9 @@
       <filters>
         <filter val="S"/>
       </filters>
+    </filterColumn>
+    <filterColumn colId="14">
+      <filters blank="1"/>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P298">
       <sortCondition ref="F1"/>
@@ -22142,7 +22165,7 @@
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
       <c r="N2" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B2, $C$2:$C$692, C2, $D$2:$D$692, D2, $E$2:$E$692, E2) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N2:N65" si="0">IF(COUNTIFS( $B$2:$B$692, B2, $C$2:$C$692, C2, $D$2:$D$692, D2, $E$2:$E$692, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
@@ -22183,7 +22206,7 @@
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
       <c r="N3" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B3, $C$2:$C$692, C3, $D$2:$D$692, D3, $E$2:$E$692, E3) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O3" s="10"/>
@@ -22231,7 +22254,7 @@
         <v>34175</v>
       </c>
       <c r="N4" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B4, $C$2:$C$692, C4, $D$2:$D$692, D4, $E$2:$E$692, E4) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O4" s="10"/>
@@ -22272,7 +22295,7 @@
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
       <c r="N5" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B5, $C$2:$C$692, C5, $D$2:$D$692, D5, $E$2:$E$692, E5) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O5" s="10"/>
@@ -22311,7 +22334,7 @@
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B6, $C$2:$C$692, C6, $D$2:$D$692, D6, $E$2:$E$692, E6) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O6" s="25"/>
@@ -22352,7 +22375,7 @@
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
       <c r="N7" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B7, $C$2:$C$692, C7, $D$2:$D$692, D7, $E$2:$E$692, E7) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O7" s="10"/>
@@ -22400,7 +22423,7 @@
         <v>350</v>
       </c>
       <c r="N8" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B8, $C$2:$C$692, C8, $D$2:$D$692, D8, $E$2:$E$692, E8) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
@@ -22439,7 +22462,7 @@
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
       <c r="N9" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B9, $C$2:$C$692, C9, $D$2:$D$692, D9, $E$2:$E$692, E9) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O9" s="19"/>
@@ -22480,7 +22503,7 @@
       <c r="L10" s="17"/>
       <c r="M10" s="17"/>
       <c r="N10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B10, $C$2:$C$692, C10, $D$2:$D$692, D10, $E$2:$E$692, E10) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22519,7 +22542,7 @@
       <c r="L11" s="17"/>
       <c r="M11" s="17"/>
       <c r="N11" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B11, $C$2:$C$692, C11, $D$2:$D$692, D11, $E$2:$E$692, E11) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22565,7 +22588,7 @@
         <v>500</v>
       </c>
       <c r="N12" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B12, $C$2:$C$692, C12, $D$2:$D$692, D12, $E$2:$E$692, E12) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O12" s="10"/>
@@ -22604,7 +22627,7 @@
       <c r="L13" s="17"/>
       <c r="M13" s="17"/>
       <c r="N13" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B13, $C$2:$C$692, C13, $D$2:$D$692, D13, $E$2:$E$692, E13) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O13" s="10"/>
@@ -22643,7 +22666,7 @@
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
       <c r="N14" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B14, $C$2:$C$692, C14, $D$2:$D$692, D14, $E$2:$E$692, E14) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O14" s="10"/>
@@ -22684,7 +22707,7 @@
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
       <c r="N15" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B15, $C$2:$C$692, C15, $D$2:$D$692, D15, $E$2:$E$692, E15) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22723,7 +22746,7 @@
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
       <c r="N16" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B16, $C$2:$C$692, C16, $D$2:$D$692, D16, $E$2:$E$692, E16) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O16"/>
@@ -22764,7 +22787,7 @@
       <c r="L17" s="17"/>
       <c r="M17" s="17"/>
       <c r="N17" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B17, $C$2:$C$692, C17, $D$2:$D$692, D17, $E$2:$E$692, E17) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O17"/>
@@ -22805,7 +22828,7 @@
       <c r="L18" s="17"/>
       <c r="M18" s="17"/>
       <c r="N18" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B18, $C$2:$C$692, C18, $D$2:$D$692, D18, $E$2:$E$692, E18) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22842,7 +22865,7 @@
       <c r="L19" s="17"/>
       <c r="M19" s="17"/>
       <c r="N19" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B19, $C$2:$C$692, C19, $D$2:$D$692, D19, $E$2:$E$692, E19) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O19"/>
@@ -22881,7 +22904,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="17"/>
       <c r="N20" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B20, $C$2:$C$692, C20, $D$2:$D$692, D20, $E$2:$E$692, E20) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O20"/>
@@ -22928,7 +22951,7 @@
         <v>516</v>
       </c>
       <c r="N21" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B21, $C$2:$C$692, C21, $D$2:$D$692, D21, $E$2:$E$692, E21) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O21" s="10"/>
@@ -22976,7 +22999,7 @@
         <v>300</v>
       </c>
       <c r="N22" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B22, $C$2:$C$692, C22, $D$2:$D$692, D22, $E$2:$E$692, E22) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P22" s="24"/>
@@ -23016,7 +23039,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="17"/>
       <c r="N23" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B23, $C$2:$C$692, C23, $D$2:$D$692, D23, $E$2:$E$692, E23) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O23"/>
@@ -23057,7 +23080,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
       <c r="N24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B24, $C$2:$C$692, C24, $D$2:$D$692, D24, $E$2:$E$692, E24) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O24"/>
@@ -23098,7 +23121,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B25, $C$2:$C$692, C25, $D$2:$D$692, D25, $E$2:$E$692, E25) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O25"/>
@@ -23138,7 +23161,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B26, $C$2:$C$692, C26, $D$2:$D$692, D26, $E$2:$E$692, E26) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O26"/>
@@ -23186,7 +23209,7 @@
         <v>300</v>
       </c>
       <c r="N27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B27, $C$2:$C$692, C27, $D$2:$D$692, D27, $E$2:$E$692, E27) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23223,7 +23246,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
       <c r="N28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B28, $C$2:$C$692, C28, $D$2:$D$692, D28, $E$2:$E$692, E28) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O28"/>
@@ -23270,7 +23293,7 @@
         <v>554</v>
       </c>
       <c r="N29" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B29, $C$2:$C$692, C29, $D$2:$D$692, D29, $E$2:$E$692, E29) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23309,7 +23332,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
       <c r="N30" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B30, $C$2:$C$692, C30, $D$2:$D$692, D30, $E$2:$E$692, E30) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O30"/>
@@ -23358,7 +23381,7 @@
         <v>225</v>
       </c>
       <c r="N31" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B31, $C$2:$C$692, C31, $D$2:$D$692, D31, $E$2:$E$692, E31) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23397,7 +23420,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="17"/>
       <c r="N32" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B32, $C$2:$C$692, C32, $D$2:$D$692, D32, $E$2:$E$692, E32) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P32"/>
@@ -23444,7 +23467,7 @@
         <v>646</v>
       </c>
       <c r="N33" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B33, $C$2:$C$692, C33, $D$2:$D$692, D33, $E$2:$E$692, E33) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O33" s="10"/>
@@ -23485,7 +23508,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="17"/>
       <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B34, $C$2:$C$692, C34, $D$2:$D$692, D34, $E$2:$E$692, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O34"/>
@@ -23526,7 +23549,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="17"/>
       <c r="N35" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B35, $C$2:$C$692, C35, $D$2:$D$692, D35, $E$2:$E$692, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23563,7 +23586,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
       <c r="N36" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B36, $C$2:$C$692, C36, $D$2:$D$692, D36, $E$2:$E$692, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O36"/>
@@ -23602,7 +23625,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="17"/>
       <c r="N37" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B37, $C$2:$C$692, C37, $D$2:$D$692, D37, $E$2:$E$692, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O37"/>
@@ -23643,7 +23666,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="17"/>
       <c r="N38" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B38, $C$2:$C$692, C38, $D$2:$D$692, D38, $E$2:$E$692, E38) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O38"/>
@@ -23682,7 +23705,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B39, $C$2:$C$692, C39, $D$2:$D$692, D39, $E$2:$E$692, E39) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O39"/>
@@ -23730,7 +23753,7 @@
         <v>314</v>
       </c>
       <c r="N40" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B40, $C$2:$C$692, C40, $D$2:$D$692, D40, $E$2:$E$692, E40) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -23776,7 +23799,7 @@
         <v>300</v>
       </c>
       <c r="N41" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B41, $C$2:$C$692, C41, $D$2:$D$692, D41, $E$2:$E$692, E41) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O41"/>
@@ -23815,7 +23838,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B42, $C$2:$C$692, C42, $D$2:$D$692, D42, $E$2:$E$692, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O42"/>
@@ -23854,7 +23877,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B43, $C$2:$C$692, C43, $D$2:$D$692, D43, $E$2:$E$692, E43) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O43"/>
@@ -23893,7 +23916,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="17"/>
       <c r="N44" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B44, $C$2:$C$692, C44, $D$2:$D$692, D44, $E$2:$E$692, E44) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O44"/>
@@ -23934,7 +23957,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="17"/>
       <c r="N45" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B45, $C$2:$C$692, C45, $D$2:$D$692, D45, $E$2:$E$692, E45) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O45"/>
@@ -23973,7 +23996,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="17"/>
       <c r="N46" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B46, $C$2:$C$692, C46, $D$2:$D$692, D46, $E$2:$E$692, E46) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O46"/>
@@ -24012,7 +24035,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="17"/>
       <c r="N47" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B47, $C$2:$C$692, C47, $D$2:$D$692, D47, $E$2:$E$692, E47) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O47"/>
@@ -24055,7 +24078,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="17"/>
       <c r="N48" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B48, $C$2:$C$692, C48, $D$2:$D$692, D48, $E$2:$E$692, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24102,7 +24125,7 @@
         <v>540</v>
       </c>
       <c r="N49" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B49, $C$2:$C$692, C49, $D$2:$D$692, D49, $E$2:$E$692, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24148,7 +24171,7 @@
         <v>240</v>
       </c>
       <c r="N50" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B50, $C$2:$C$692, C50, $D$2:$D$692, D50, $E$2:$E$692, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O50" s="10"/>
@@ -24192,7 +24215,7 @@
         <v>3156</v>
       </c>
       <c r="N51" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B51, $C$2:$C$692, C51, $D$2:$D$692, D51, $E$2:$E$692, E51) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O51" s="10"/>
@@ -24240,7 +24263,7 @@
         <v>500</v>
       </c>
       <c r="N52" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B52, $C$2:$C$692, C52, $D$2:$D$692, D52, $E$2:$E$692, E52) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O52" s="10"/>
@@ -24279,7 +24302,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="17"/>
       <c r="N53" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B53, $C$2:$C$692, C53, $D$2:$D$692, D53, $E$2:$E$692, E53) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24316,7 +24339,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="17"/>
       <c r="N54" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B54, $C$2:$C$692, C54, $D$2:$D$692, D54, $E$2:$E$692, E54) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O54"/>
@@ -24355,7 +24378,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="17"/>
       <c r="N55" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B55, $C$2:$C$692, C55, $D$2:$D$692, D55, $E$2:$E$692, E55) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O55"/>
@@ -24394,7 +24417,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="17"/>
       <c r="N56" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B56, $C$2:$C$692, C56, $D$2:$D$692, D56, $E$2:$E$692, E56) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O56"/>
@@ -24433,7 +24456,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B57, $C$2:$C$692, C57, $D$2:$D$692, D57, $E$2:$E$692, E57) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O57"/>
@@ -24474,7 +24497,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="17"/>
       <c r="N58" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B58, $C$2:$C$692, C58, $D$2:$D$692, D58, $E$2:$E$692, E58) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O58"/>
@@ -24522,7 +24545,7 @@
         <v>1200</v>
       </c>
       <c r="N59" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B59, $C$2:$C$692, C59, $D$2:$D$692, D59, $E$2:$E$692, E59) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O59" s="38" t="s">
@@ -24564,7 +24587,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="17"/>
       <c r="N60" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B60, $C$2:$C$692, C60, $D$2:$D$692, D60, $E$2:$E$692, E60) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O60"/>
@@ -24612,7 +24635,7 @@
         <v>10680</v>
       </c>
       <c r="N61" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B61, $C$2:$C$692, C61, $D$2:$D$692, D61, $E$2:$E$692, E61) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O61" s="10"/>
@@ -24653,7 +24676,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="17"/>
       <c r="N62" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B62, $C$2:$C$692, C62, $D$2:$D$692, D62, $E$2:$E$692, E62) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O62"/>
@@ -24701,7 +24724,7 @@
         <v>650</v>
       </c>
       <c r="N63" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B63, $C$2:$C$692, C63, $D$2:$D$692, D63, $E$2:$E$692, E63) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24740,7 +24763,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="17"/>
       <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B64, $C$2:$C$692, C64, $D$2:$D$692, D64, $E$2:$E$692, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O64"/>
@@ -24788,7 +24811,7 @@
         <v>10880</v>
       </c>
       <c r="N65" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B65, $C$2:$C$692, C65, $D$2:$D$692, D65, $E$2:$E$692, E65) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24834,7 +24857,7 @@
         <v>1000</v>
       </c>
       <c r="N66" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B66, $C$2:$C$692, C66, $D$2:$D$692, D66, $E$2:$E$692, E66) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N66:N129" si="1">IF(COUNTIFS( $B$2:$B$692, B66, $C$2:$C$692, C66, $D$2:$D$692, D66, $E$2:$E$692, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -24880,7 +24903,7 @@
         <v>288</v>
       </c>
       <c r="N67" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B67, $C$2:$C$692, C67, $D$2:$D$692, D67, $E$2:$E$692, E67) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -24926,7 +24949,7 @@
         <v>360</v>
       </c>
       <c r="N68" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B68, $C$2:$C$692, C68, $D$2:$D$692, D68, $E$2:$E$692, E68) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O68" s="38" t="s">
@@ -24975,7 +24998,7 @@
         <v>300</v>
       </c>
       <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B69, $C$2:$C$692, C69, $D$2:$D$692, D69, $E$2:$E$692, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O69" s="10"/>
@@ -25016,7 +25039,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="17"/>
       <c r="N70" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B70, $C$2:$C$692, C70, $D$2:$D$692, D70, $E$2:$E$692, E70) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O70"/>
@@ -25060,11 +25083,11 @@
         <v>16755</v>
       </c>
       <c r="M71" s="18">
-        <f t="shared" ref="M71:M76" si="0">ABS((D71*E71)-L71)</f>
+        <f t="shared" ref="M71:M76" si="2">ABS((D71*E71)-L71)</f>
         <v>295</v>
       </c>
       <c r="N71" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B71, $C$2:$C$692, C71, $D$2:$D$692, D71, $E$2:$E$692, E71) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25106,11 +25129,11 @@
         <v>4640</v>
       </c>
       <c r="M72" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N72" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B72, $C$2:$C$692, C72, $D$2:$D$692, D72, $E$2:$E$692, E72) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O72" s="38" t="s">
@@ -25155,11 +25178,11 @@
         <v>33200</v>
       </c>
       <c r="M73" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1200</v>
       </c>
       <c r="N73" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B73, $C$2:$C$692, C73, $D$2:$D$692, D73, $E$2:$E$692, E73) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25201,11 +25224,11 @@
         <v>19550</v>
       </c>
       <c r="M74" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>650</v>
       </c>
       <c r="N74" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B74, $C$2:$C$692, C74, $D$2:$D$692, D74, $E$2:$E$692, E74) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -25247,11 +25270,11 @@
         <v>8420</v>
       </c>
       <c r="M75" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N75" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B75, $C$2:$C$692, C75, $D$2:$D$692, D75, $E$2:$E$692, E75) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O75" s="10"/>
@@ -25295,11 +25318,11 @@
         <v>6367.2</v>
       </c>
       <c r="M76" s="18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>300.80000000000018</v>
       </c>
       <c r="N76" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B76, $C$2:$C$692, C76, $D$2:$D$692, D76, $E$2:$E$692, E76) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O76" s="38" t="s">
@@ -25340,7 +25363,7 @@
       <c r="L77" s="17"/>
       <c r="M77" s="17"/>
       <c r="N77" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B77, $C$2:$C$692, C77, $D$2:$D$692, D77, $E$2:$E$692, E77) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O77"/>
@@ -25384,11 +25407,11 @@
         <v>8570</v>
       </c>
       <c r="M78" s="27">
-        <f t="shared" ref="M78:M96" si="1">ABS((D78*E78)-L78)</f>
+        <f t="shared" ref="M78:M96" si="3">ABS((D78*E78)-L78)</f>
         <v>650</v>
       </c>
       <c r="N78" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B78, $C$2:$C$692, C78, $D$2:$D$692, D78, $E$2:$E$692, E78) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O78" s="38" t="s">
@@ -25433,11 +25456,11 @@
         <v>39300</v>
       </c>
       <c r="M79" s="18">
+        <f t="shared" si="3"/>
+        <v>18850</v>
+      </c>
+      <c r="N79" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>18850</v>
-      </c>
-      <c r="N79" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B79, $C$2:$C$692, C79, $D$2:$D$692, D79, $E$2:$E$692, E79) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25479,11 +25502,11 @@
         <v>8400</v>
       </c>
       <c r="M80" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N80" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N80" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B80, $C$2:$C$692, C80, $D$2:$D$692, D80, $E$2:$E$692, E80) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25525,11 +25548,11 @@
         <v>10250</v>
       </c>
       <c r="M81" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N81" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N81" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B81, $C$2:$C$692, C81, $D$2:$D$692, D81, $E$2:$E$692, E81) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25571,11 +25594,11 @@
         <v>35200</v>
       </c>
       <c r="M82" s="18">
+        <f t="shared" si="3"/>
+        <v>720</v>
+      </c>
+      <c r="N82" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>720</v>
-      </c>
-      <c r="N82" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B82, $C$2:$C$692, C82, $D$2:$D$692, D82, $E$2:$E$692, E82) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25617,11 +25640,11 @@
         <v>3560</v>
       </c>
       <c r="M83" s="18">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="N83" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="N83" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B83, $C$2:$C$692, C83, $D$2:$D$692, D83, $E$2:$E$692, E83) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25663,11 +25686,11 @@
         <v>33950</v>
       </c>
       <c r="M84" s="18">
+        <f t="shared" si="3"/>
+        <v>850</v>
+      </c>
+      <c r="N84" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>850</v>
-      </c>
-      <c r="N84" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B84, $C$2:$C$692, C84, $D$2:$D$692, D84, $E$2:$E$692, E84) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25709,11 +25732,11 @@
         <v>11660</v>
       </c>
       <c r="M85" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N85" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N85" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B85, $C$2:$C$692, C85, $D$2:$D$692, D85, $E$2:$E$692, E85) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O85" s="38" t="s">
@@ -25758,11 +25781,11 @@
         <v>15300</v>
       </c>
       <c r="M86" s="18">
+        <f t="shared" si="3"/>
+        <v>420</v>
+      </c>
+      <c r="N86" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>420</v>
-      </c>
-      <c r="N86" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B86, $C$2:$C$692, C86, $D$2:$D$692, D86, $E$2:$E$692, E86) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25804,11 +25827,11 @@
         <v>5450</v>
       </c>
       <c r="M87" s="18">
+        <f t="shared" si="3"/>
+        <v>295</v>
+      </c>
+      <c r="N87" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>295</v>
-      </c>
-      <c r="N87" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B87, $C$2:$C$692, C87, $D$2:$D$692, D87, $E$2:$E$692, E87) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O87" s="10"/>
@@ -25852,11 +25875,11 @@
         <v>17150</v>
       </c>
       <c r="M88" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N88" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N88" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B88, $C$2:$C$692, C88, $D$2:$D$692, D88, $E$2:$E$692, E88) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25898,11 +25921,11 @@
         <v>14130</v>
       </c>
       <c r="M89" s="18">
+        <f t="shared" si="3"/>
+        <v>714</v>
+      </c>
+      <c r="N89" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>714</v>
-      </c>
-      <c r="N89" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B89, $C$2:$C$692, C89, $D$2:$D$692, D89, $E$2:$E$692, E89) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25945,11 +25968,11 @@
         <v>8870</v>
       </c>
       <c r="M90" s="18">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="N90" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>200</v>
-      </c>
-      <c r="N90" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B90, $C$2:$C$692, C90, $D$2:$D$692, D90, $E$2:$E$692, E90) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -25991,11 +26014,11 @@
         <v>19730.5</v>
       </c>
       <c r="M91" s="27">
+        <f t="shared" si="3"/>
+        <v>504.5</v>
+      </c>
+      <c r="N91" s="29" t="str">
         <f t="shared" si="1"/>
-        <v>504.5</v>
-      </c>
-      <c r="N91" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B91, $C$2:$C$692, C91, $D$2:$D$692, D91, $E$2:$E$692, E91) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O91" s="38" t="s">
@@ -26041,11 +26064,11 @@
         <v>19690</v>
       </c>
       <c r="M92" s="27">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+      <c r="N92" s="29" t="str">
         <f t="shared" si="1"/>
-        <v>545</v>
-      </c>
-      <c r="N92" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B92, $C$2:$C$692, C92, $D$2:$D$692, D92, $E$2:$E$692, E92) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="O92" s="38" t="s">
@@ -26090,11 +26113,11 @@
         <v>10400</v>
       </c>
       <c r="M93" s="18">
+        <f t="shared" si="3"/>
+        <v>300</v>
+      </c>
+      <c r="N93" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>300</v>
-      </c>
-      <c r="N93" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B93, $C$2:$C$692, C93, $D$2:$D$692, D93, $E$2:$E$692, E93) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26136,11 +26159,11 @@
         <v>17040</v>
       </c>
       <c r="M94" s="18">
+        <f t="shared" si="3"/>
+        <v>880</v>
+      </c>
+      <c r="N94" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>880</v>
-      </c>
-      <c r="N94" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B94, $C$2:$C$692, C94, $D$2:$D$692, D94, $E$2:$E$692, E94) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O94" s="38" t="s">
@@ -26185,11 +26208,11 @@
         <v>3300</v>
       </c>
       <c r="M95" s="18">
+        <f t="shared" si="3"/>
+        <v>250</v>
+      </c>
+      <c r="N95" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>250</v>
-      </c>
-      <c r="N95" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B95, $C$2:$C$692, C95, $D$2:$D$692, D95, $E$2:$E$692, E95) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -26231,11 +26254,11 @@
         <v>10249</v>
       </c>
       <c r="M96" s="18">
+        <f t="shared" si="3"/>
+        <v>4451</v>
+      </c>
+      <c r="N96" s="10" t="str">
         <f t="shared" si="1"/>
-        <v>4451</v>
-      </c>
-      <c r="N96" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B96, $C$2:$C$692, C96, $D$2:$D$692, D96, $E$2:$E$692, E96) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O96" s="38" t="s">
@@ -26274,7 +26297,7 @@
         <v>118</v>
       </c>
       <c r="N97" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B97, $C$2:$C$692, C97, $D$2:$D$692, D97, $E$2:$E$692, E97) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26320,7 +26343,7 @@
         <v>650</v>
       </c>
       <c r="N98" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B98, $C$2:$C$692, C98, $D$2:$D$692, D98, $E$2:$E$692, E98) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26359,7 +26382,7 @@
         <v>144</v>
       </c>
       <c r="N99" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B99, $C$2:$C$692, C99, $D$2:$D$692, D99, $E$2:$E$692, E99) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26401,11 +26424,11 @@
         <v>6202</v>
       </c>
       <c r="M100" s="18">
-        <f t="shared" ref="M100:M108" si="2">ABS((D100*E100)-L100)</f>
+        <f t="shared" ref="M100:M108" si="4">ABS((D100*E100)-L100)</f>
         <v>496</v>
       </c>
       <c r="N100" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B100, $C$2:$C$692, C100, $D$2:$D$692, D100, $E$2:$E$692, E100) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26447,11 +26470,11 @@
         <v>15075</v>
       </c>
       <c r="M101" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>645</v>
       </c>
       <c r="N101" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B101, $C$2:$C$692, C101, $D$2:$D$692, D101, $E$2:$E$692, E101) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O101" s="38" t="s">
@@ -26496,11 +26519,11 @@
         <v>9886</v>
       </c>
       <c r="M102" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>654</v>
       </c>
       <c r="N102" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B102, $C$2:$C$692, C102, $D$2:$D$692, D102, $E$2:$E$692, E102) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26543,11 +26566,11 @@
         <v>8870</v>
       </c>
       <c r="M103" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N103" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B103, $C$2:$C$692, C103, $D$2:$D$692, D103, $E$2:$E$692, E103) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26589,11 +26612,11 @@
         <v>39300</v>
       </c>
       <c r="M104" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18350</v>
       </c>
       <c r="N104" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B104, $C$2:$C$692, C104, $D$2:$D$692, D104, $E$2:$E$692, E104) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26635,11 +26658,11 @@
         <v>20010</v>
       </c>
       <c r="M105" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>450</v>
       </c>
       <c r="N105" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B105, $C$2:$C$692, C105, $D$2:$D$692, D105, $E$2:$E$692, E105) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O105" s="10"/>
@@ -26683,11 +26706,11 @@
         <v>8820</v>
       </c>
       <c r="M106" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>650</v>
       </c>
       <c r="N106" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B106, $C$2:$C$692, C106, $D$2:$D$692, D106, $E$2:$E$692, E106) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26729,11 +26752,11 @@
         <v>36946</v>
       </c>
       <c r="M107" s="27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>934</v>
       </c>
       <c r="N107" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B107, $C$2:$C$692, C107, $D$2:$D$692, D107, $E$2:$E$692, E107) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O107" s="29"/>
@@ -26777,11 +26800,11 @@
         <v>20260</v>
       </c>
       <c r="M108" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>300</v>
       </c>
       <c r="N108" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B108, $C$2:$C$692, C108, $D$2:$D$692, D108, $E$2:$E$692, E108) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O108"/>
@@ -26817,7 +26840,7 @@
       </c>
       <c r="J109" s="34"/>
       <c r="N109" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B109, $C$2:$C$692, C109, $D$2:$D$692, D109, $E$2:$E$692, E109) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O109" s="29"/>
@@ -26864,7 +26887,7 @@
         <v>300</v>
       </c>
       <c r="N110" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B110, $C$2:$C$692, C110, $D$2:$D$692, D110, $E$2:$E$692, E110) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -26910,7 +26933,7 @@
         <v>710.99999999999636</v>
       </c>
       <c r="N111" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B111, $C$2:$C$692, C111, $D$2:$D$692, D111, $E$2:$E$692, E111) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P111"/>
@@ -26957,7 +26980,7 @@
         <v>1700</v>
       </c>
       <c r="N112" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B112, $C$2:$C$692, C112, $D$2:$D$692, D112, $E$2:$E$692, E112) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O112" s="29"/>
@@ -27004,7 +27027,7 @@
         <v>300</v>
       </c>
       <c r="N113" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B113, $C$2:$C$692, C113, $D$2:$D$692, D113, $E$2:$E$692, E113) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P113" s="29"/>
@@ -27039,7 +27062,7 @@
       </c>
       <c r="J114" s="34"/>
       <c r="N114" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B114, $C$2:$C$692, C114, $D$2:$D$692, D114, $E$2:$E$692, E114) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27085,7 +27108,7 @@
         <v>300</v>
       </c>
       <c r="N115" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B115, $C$2:$C$692, C115, $D$2:$D$692, D115, $E$2:$E$692, E115) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27132,7 +27155,7 @@
         <v>300</v>
       </c>
       <c r="N116" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B116, $C$2:$C$692, C116, $D$2:$D$692, D116, $E$2:$E$692, E116) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27166,7 +27189,7 @@
       </c>
       <c r="J117" s="34"/>
       <c r="N117" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B117, $C$2:$C$692, C117, $D$2:$D$692, D117, $E$2:$E$692, E117) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O117" s="38" t="s">
@@ -27216,7 +27239,7 @@
         <v>1400</v>
       </c>
       <c r="N118" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B118, $C$2:$C$692, C118, $D$2:$D$692, D118, $E$2:$E$692, E118) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O118" s="38" t="s">
@@ -27266,7 +27289,7 @@
         <v>270</v>
       </c>
       <c r="N119" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B119, $C$2:$C$692, C119, $D$2:$D$692, D119, $E$2:$E$692, E119) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O119" s="39" t="s">
@@ -27316,7 +27339,7 @@
         <v>188.60000000000014</v>
       </c>
       <c r="N120" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B120, $C$2:$C$692, C120, $D$2:$D$692, D120, $E$2:$E$692, E120) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O120" s="39" t="s">
@@ -27366,7 +27389,7 @@
         <v>280</v>
       </c>
       <c r="N121" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B121, $C$2:$C$692, C121, $D$2:$D$692, D121, $E$2:$E$692, E121) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O121" s="38" t="s">
@@ -27415,7 +27438,7 @@
         <v>376</v>
       </c>
       <c r="N122" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B122, $C$2:$C$692, C122, $D$2:$D$692, D122, $E$2:$E$692, E122) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27454,7 +27477,7 @@
       <c r="L123" s="18"/>
       <c r="M123" s="18"/>
       <c r="N123" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B123, $C$2:$C$692, C123, $D$2:$D$692, D123, $E$2:$E$692, E123) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O123" s="10"/>
@@ -27495,7 +27518,7 @@
       <c r="L124" s="17"/>
       <c r="M124" s="17"/>
       <c r="N124" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B124, $C$2:$C$692, C124, $D$2:$D$692, D124, $E$2:$E$692, E124) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O124"/>
@@ -27543,7 +27566,7 @@
         <v>500</v>
       </c>
       <c r="N125" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B125, $C$2:$C$692, C125, $D$2:$D$692, D125, $E$2:$E$692, E125) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27579,7 +27602,7 @@
         <v>118</v>
       </c>
       <c r="N126" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B126, $C$2:$C$692, C126, $D$2:$D$692, D126, $E$2:$E$692, E126) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27613,7 +27636,7 @@
       </c>
       <c r="J127" s="34"/>
       <c r="N127" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B127, $C$2:$C$692, C127, $D$2:$D$692, D127, $E$2:$E$692, E127) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27659,7 +27682,7 @@
         <v>1000</v>
       </c>
       <c r="N128" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B128, $C$2:$C$692, C128, $D$2:$D$692, D128, $E$2:$E$692, E128) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O128" s="10"/>
@@ -27697,7 +27720,7 @@
         <v>118</v>
       </c>
       <c r="N129" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B129, $C$2:$C$692, C129, $D$2:$D$692, D129, $E$2:$E$692, E129) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P129"/>
@@ -27732,7 +27755,7 @@
       </c>
       <c r="J130" s="34"/>
       <c r="N130" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B130, $C$2:$C$692, C130, $D$2:$D$692, D130, $E$2:$E$692, E130) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N130:N193" si="5">IF(COUNTIFS( $B$2:$B$692, B130, $C$2:$C$692, C130, $D$2:$D$692, D130, $E$2:$E$692, E130) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -27778,7 +27801,7 @@
         <v>290</v>
       </c>
       <c r="N131" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B131, $C$2:$C$692, C131, $D$2:$D$692, D131, $E$2:$E$692, E131) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O131" s="10"/>
@@ -27816,7 +27839,7 @@
         <v>117</v>
       </c>
       <c r="N132" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B132, $C$2:$C$692, C132, $D$2:$D$692, D132, $E$2:$E$692, E132) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -27858,11 +27881,11 @@
         <v>10410</v>
       </c>
       <c r="M133" s="18">
-        <f t="shared" ref="M133:M139" si="3">ABS((D133*E133)-L133)</f>
+        <f t="shared" ref="M133:M139" si="6">ABS((D133*E133)-L133)</f>
         <v>300</v>
       </c>
       <c r="N133" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B133, $C$2:$C$692, C133, $D$2:$D$692, D133, $E$2:$E$692, E133) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O133" s="29"/>
@@ -27905,11 +27928,11 @@
         <v>14552</v>
       </c>
       <c r="M134" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>300</v>
       </c>
       <c r="N134" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B134, $C$2:$C$692, C134, $D$2:$D$692, D134, $E$2:$E$692, E134) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O134" s="38" t="s">
@@ -27955,11 +27978,11 @@
         <v>3400</v>
       </c>
       <c r="M135" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>250</v>
       </c>
       <c r="N135" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B135, $C$2:$C$692, C135, $D$2:$D$692, D135, $E$2:$E$692, E135) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28001,11 +28024,11 @@
         <v>5370</v>
       </c>
       <c r="M136" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>320</v>
       </c>
       <c r="N136" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B136, $C$2:$C$692, C136, $D$2:$D$692, D136, $E$2:$E$692, E136) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28047,11 +28070,11 @@
         <v>2610</v>
       </c>
       <c r="M137" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>235</v>
       </c>
       <c r="N137" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B137, $C$2:$C$692, C137, $D$2:$D$692, D137, $E$2:$E$692, E137) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28093,11 +28116,11 @@
         <v>9170</v>
       </c>
       <c r="M138" s="27">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>200</v>
       </c>
       <c r="N138" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B138, $C$2:$C$692, C138, $D$2:$D$692, D138, $E$2:$E$692, E138) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O138" s="38" t="s">
@@ -28142,11 +28165,11 @@
         <v>14200</v>
       </c>
       <c r="M139" s="18">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>500</v>
       </c>
       <c r="N139" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B139, $C$2:$C$692, C139, $D$2:$D$692, D139, $E$2:$E$692, E139) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28180,7 +28203,7 @@
       </c>
       <c r="J140" s="34"/>
       <c r="N140" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B140, $C$2:$C$692, C140, $D$2:$D$692, D140, $E$2:$E$692, E140) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O140" s="24"/>
@@ -28215,7 +28238,7 @@
       </c>
       <c r="J141" s="34"/>
       <c r="N141" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B141, $C$2:$C$692, C141, $D$2:$D$692, D141, $E$2:$E$692, E141) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28249,7 +28272,7 @@
       </c>
       <c r="J142" s="34"/>
       <c r="N142" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B142, $C$2:$C$692, C142, $D$2:$D$692, D142, $E$2:$E$692, E142) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28291,11 +28314,11 @@
         <v>5520</v>
       </c>
       <c r="M143" s="27">
-        <f t="shared" ref="M143:M149" si="4">ABS((D143*E143)-L143)</f>
+        <f t="shared" ref="M143:M149" si="7">ABS((D143*E143)-L143)</f>
         <v>300</v>
       </c>
       <c r="N143" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B143, $C$2:$C$692, C143, $D$2:$D$692, D143, $E$2:$E$692, E143) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O143" s="38" t="s">
@@ -28340,11 +28363,11 @@
         <v>2657</v>
       </c>
       <c r="M144" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>253</v>
       </c>
       <c r="N144" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B144, $C$2:$C$692, C144, $D$2:$D$692, D144, $E$2:$E$692, E144) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O144" s="38" t="s">
@@ -28389,11 +28412,11 @@
         <v>2554.5</v>
       </c>
       <c r="M145" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>355.5</v>
       </c>
       <c r="N145" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B145, $C$2:$C$692, C145, $D$2:$D$692, D145, $E$2:$E$692, E145) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O145" s="38" t="s">
@@ -28439,11 +28462,11 @@
         <v>5585</v>
       </c>
       <c r="M146" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>395</v>
       </c>
       <c r="N146" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B146, $C$2:$C$692, C146, $D$2:$D$692, D146, $E$2:$E$692, E146) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O146" s="38" t="s">
@@ -28489,11 +28512,11 @@
         <v>5730</v>
       </c>
       <c r="M147" s="27">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>250</v>
       </c>
       <c r="N147" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B147, $C$2:$C$692, C147, $D$2:$D$692, D147, $E$2:$E$692, E147) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
       <c r="O147" s="38" t="s">
@@ -28538,11 +28561,11 @@
         <v>5940</v>
       </c>
       <c r="M148" s="18">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>300</v>
       </c>
       <c r="N148" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B148, $C$2:$C$692, C148, $D$2:$D$692, D148, $E$2:$E$692, E148) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O148" s="10"/>
@@ -28586,11 +28609,11 @@
         <v>16580</v>
       </c>
       <c r="M149" s="44">
-        <f t="shared" si="4"/>
+        <f t="shared" si="7"/>
         <v>660</v>
       </c>
       <c r="N149" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B149, $C$2:$C$692, C149, $D$2:$D$692, D149, $E$2:$E$692, E149) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O149" s="24"/>
@@ -28630,7 +28653,7 @@
         <v>118</v>
       </c>
       <c r="N150" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B150, $C$2:$C$692, C150, $D$2:$D$692, D150, $E$2:$E$692, E150) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28669,7 +28692,7 @@
       <c r="L151" s="17"/>
       <c r="M151" s="17"/>
       <c r="N151" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B151, $C$2:$C$692, C151, $D$2:$D$692, D151, $E$2:$E$692, E151) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O151"/>
@@ -28717,7 +28740,7 @@
         <v>300</v>
       </c>
       <c r="N152" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B152, $C$2:$C$692, C152, $D$2:$D$692, D152, $E$2:$E$692, E152) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28763,7 +28786,7 @@
         <v>940</v>
       </c>
       <c r="N153" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B153, $C$2:$C$692, C153, $D$2:$D$692, D153, $E$2:$E$692, E153) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28799,7 +28822,7 @@
         <v>118</v>
       </c>
       <c r="N154" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B154, $C$2:$C$692, C154, $D$2:$D$692, D154, $E$2:$E$692, E154) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28845,7 +28868,7 @@
         <v>300</v>
       </c>
       <c r="N155" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B155, $C$2:$C$692, C155, $D$2:$D$692, D155, $E$2:$E$692, E155) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -28891,7 +28914,7 @@
         <v>275</v>
       </c>
       <c r="N156" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B156, $C$2:$C$692, C156, $D$2:$D$692, D156, $E$2:$E$692, E156) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28937,7 +28960,7 @@
         <v>225</v>
       </c>
       <c r="N157" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B157, $C$2:$C$692, C157, $D$2:$D$692, D157, $E$2:$E$692, E157) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -28983,7 +29006,7 @@
         <v>300</v>
       </c>
       <c r="N158" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B158, $C$2:$C$692, C158, $D$2:$D$692, D158, $E$2:$E$692, E158) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O158"/>
@@ -29030,7 +29053,7 @@
         <v>527.5</v>
       </c>
       <c r="N159" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B159, $C$2:$C$692, C159, $D$2:$D$692, D159, $E$2:$E$692, E159) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29071,7 +29094,7 @@
       <c r="L160" s="27"/>
       <c r="M160" s="27"/>
       <c r="N160" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B160, $C$2:$C$692, C160, $D$2:$D$692, D160, $E$2:$E$692, E160) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O160" s="29"/>
@@ -29119,7 +29142,7 @@
         <v>500</v>
       </c>
       <c r="N161" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B161, $C$2:$C$692, C161, $D$2:$D$692, D161, $E$2:$E$692, E161) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29155,7 +29178,7 @@
         <v>118</v>
       </c>
       <c r="N162" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B162, $C$2:$C$692, C162, $D$2:$D$692, D162, $E$2:$E$692, E162) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29201,7 +29224,7 @@
         <v>800</v>
       </c>
       <c r="N163" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B163, $C$2:$C$692, C163, $D$2:$D$692, D163, $E$2:$E$692, E163) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29238,7 +29261,7 @@
       <c r="L164" s="18"/>
       <c r="M164" s="18"/>
       <c r="N164" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B164, $C$2:$C$692, C164, $D$2:$D$692, D164, $E$2:$E$692, E164) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O164" s="10"/>
@@ -29274,7 +29297,7 @@
       </c>
       <c r="J165" s="34"/>
       <c r="N165" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B165, $C$2:$C$692, C165, $D$2:$D$692, D165, $E$2:$E$692, E165) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P165" s="29"/>
@@ -29321,7 +29344,7 @@
         <v>810</v>
       </c>
       <c r="N166" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B166, $C$2:$C$692, C166, $D$2:$D$692, D166, $E$2:$E$692, E166) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29367,7 +29390,7 @@
         <v>300</v>
       </c>
       <c r="N167" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B167, $C$2:$C$692, C167, $D$2:$D$692, D167, $E$2:$E$692, E167) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29413,7 +29436,7 @@
         <v>300</v>
       </c>
       <c r="N168" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B168, $C$2:$C$692, C168, $D$2:$D$692, D168, $E$2:$E$692, E168) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P168" s="19"/>
@@ -29460,7 +29483,7 @@
         <v>501</v>
       </c>
       <c r="N169" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B169, $C$2:$C$692, C169, $D$2:$D$692, D169, $E$2:$E$692, E169) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O169" s="38" t="s">
@@ -29509,7 +29532,7 @@
         <v>650</v>
       </c>
       <c r="N170" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B170, $C$2:$C$692, C170, $D$2:$D$692, D170, $E$2:$E$692, E170) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O170" s="29"/>
@@ -29546,7 +29569,7 @@
         <v>194</v>
       </c>
       <c r="N171" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B171, $C$2:$C$692, C171, $D$2:$D$692, D171, $E$2:$E$692, E171) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29592,7 +29615,7 @@
         <v>450</v>
       </c>
       <c r="N172" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B172, $C$2:$C$692, C172, $D$2:$D$692, D172, $E$2:$E$692, E172) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29638,7 +29661,7 @@
         <v>300</v>
       </c>
       <c r="N173" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B173, $C$2:$C$692, C173, $D$2:$D$692, D173, $E$2:$E$692, E173) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29674,7 +29697,7 @@
         <v>117</v>
       </c>
       <c r="N174" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B174, $C$2:$C$692, C174, $D$2:$D$692, D174, $E$2:$E$692, E174) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29720,7 +29743,7 @@
         <v>646</v>
       </c>
       <c r="N175" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B175, $C$2:$C$692, C175, $D$2:$D$692, D175, $E$2:$E$692, E175) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O175" s="38" t="s">
@@ -29757,7 +29780,7 @@
       </c>
       <c r="J176" s="34"/>
       <c r="N176" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B176, $C$2:$C$692, C176, $D$2:$D$692, D176, $E$2:$E$692, E176) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29793,7 +29816,7 @@
         <v>118</v>
       </c>
       <c r="N177" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B177, $C$2:$C$692, C177, $D$2:$D$692, D177, $E$2:$E$692, E177) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O177" s="29"/>
@@ -29828,7 +29851,7 @@
       </c>
       <c r="J178" s="34"/>
       <c r="N178" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B178, $C$2:$C$692, C178, $D$2:$D$692, D178, $E$2:$E$692, E178) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -29874,7 +29897,7 @@
         <v>500</v>
       </c>
       <c r="N179" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B179, $C$2:$C$692, C179, $D$2:$D$692, D179, $E$2:$E$692, E179) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O179" s="39" t="s">
@@ -29913,7 +29936,7 @@
         <v>118</v>
       </c>
       <c r="N180" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B180, $C$2:$C$692, C180, $D$2:$D$692, D180, $E$2:$E$692, E180) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O180" s="38" t="s">
@@ -29962,7 +29985,7 @@
         <v>650</v>
       </c>
       <c r="N181" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B181, $C$2:$C$692, C181, $D$2:$D$692, D181, $E$2:$E$692, E181) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P181" s="29"/>
@@ -30009,7 +30032,7 @@
         <v>300</v>
       </c>
       <c r="N182" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B182, $C$2:$C$692, C182, $D$2:$D$692, D182, $E$2:$E$692, E182) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30048,7 +30071,7 @@
       <c r="L183" s="18"/>
       <c r="M183" s="18"/>
       <c r="N183" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B183, $C$2:$C$692, C183, $D$2:$D$692, D183, $E$2:$E$692, E183) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O183" s="10"/>
@@ -30092,11 +30115,11 @@
         <v>8049</v>
       </c>
       <c r="M184" s="18">
-        <f t="shared" ref="M184:M189" si="5">ABS((D184*E184)-L184)</f>
+        <f t="shared" ref="M184:M189" si="8">ABS((D184*E184)-L184)</f>
         <v>800</v>
       </c>
       <c r="N184" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B184, $C$2:$C$692, C184, $D$2:$D$692, D184, $E$2:$E$692, E184) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O184" s="38" t="s">
@@ -30141,11 +30164,11 @@
         <v>4680</v>
       </c>
       <c r="M185" s="27">
+        <f t="shared" si="8"/>
+        <v>140</v>
+      </c>
+      <c r="N185" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>140</v>
-      </c>
-      <c r="N185" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B185, $C$2:$C$692, C185, $D$2:$D$692, D185, $E$2:$E$692, E185) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
       <c r="P185" s="29"/>
@@ -30188,11 +30211,11 @@
         <v>4520</v>
       </c>
       <c r="M186" s="27">
+        <f t="shared" si="8"/>
+        <v>300</v>
+      </c>
+      <c r="N186" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>300</v>
-      </c>
-      <c r="N186" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B186, $C$2:$C$692, C186, $D$2:$D$692, D186, $E$2:$E$692, E186) &gt; 1, "Duplicate", "Unique")</f>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30234,11 +30257,11 @@
         <v>5905</v>
       </c>
       <c r="M187" s="18">
+        <f t="shared" si="8"/>
+        <v>275</v>
+      </c>
+      <c r="N187" t="str">
         <f t="shared" si="5"/>
-        <v>275</v>
-      </c>
-      <c r="N187" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B187, $C$2:$C$692, C187, $D$2:$D$692, D187, $E$2:$E$692, E187) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -30280,11 +30303,11 @@
         <v>11175</v>
       </c>
       <c r="M188" s="27">
+        <f t="shared" si="8"/>
+        <v>300</v>
+      </c>
+      <c r="N188" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>300</v>
-      </c>
-      <c r="N188" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B188, $C$2:$C$692, C188, $D$2:$D$692, D188, $E$2:$E$692, E188) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O188" s="29"/>
@@ -30328,11 +30351,11 @@
         <v>4402</v>
       </c>
       <c r="M189" s="27">
+        <f t="shared" si="8"/>
+        <v>188</v>
+      </c>
+      <c r="N189" s="29" t="str">
         <f t="shared" si="5"/>
-        <v>188</v>
-      </c>
-      <c r="N189" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B189, $C$2:$C$692, C189, $D$2:$D$692, D189, $E$2:$E$692, E189) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O189" s="29"/>
@@ -30373,7 +30396,7 @@
       <c r="L190" s="44"/>
       <c r="M190" s="44"/>
       <c r="N190" s="24" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B190, $C$2:$C$692, C190, $D$2:$D$692, D190, $E$2:$E$692, E190) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O190" s="24"/>
@@ -30411,7 +30434,7 @@
       </c>
       <c r="J191" s="34"/>
       <c r="N191" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B191, $C$2:$C$692, C191, $D$2:$D$692, D191, $E$2:$E$692, E191) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30457,7 +30480,7 @@
         <v>48320</v>
       </c>
       <c r="N192" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B192, $C$2:$C$692, C192, $D$2:$D$692, D192, $E$2:$E$692, E192) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="O192" s="38" t="s">
@@ -30507,7 +30530,7 @@
         <v>300</v>
       </c>
       <c r="N193" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B193, $C$2:$C$692, C193, $D$2:$D$692, D193, $E$2:$E$692, E193) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="5"/>
         <v>Unique</v>
       </c>
       <c r="P193" s="25"/>
@@ -30544,7 +30567,7 @@
         <v>118</v>
       </c>
       <c r="N194" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B194, $C$2:$C$692, C194, $D$2:$D$692, D194, $E$2:$E$692, E194) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N194:N257" si="9">IF(COUNTIFS( $B$2:$B$692, B194, $C$2:$C$692, C194, $D$2:$D$692, D194, $E$2:$E$692, E194) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O194" s="29"/>
@@ -30591,7 +30614,7 @@
         <v>300</v>
       </c>
       <c r="N195" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B195, $C$2:$C$692, C195, $D$2:$D$692, D195, $E$2:$E$692, E195) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30637,7 +30660,7 @@
         <v>250</v>
       </c>
       <c r="N196" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B196, $C$2:$C$692, C196, $D$2:$D$692, D196, $E$2:$E$692, E196) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30683,7 +30706,7 @@
         <v>294</v>
       </c>
       <c r="N197" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B197, $C$2:$C$692, C197, $D$2:$D$692, D197, $E$2:$E$692, E197) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30729,7 +30752,7 @@
         <v>294</v>
       </c>
       <c r="N198" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B198, $C$2:$C$692, C198, $D$2:$D$692, D198, $E$2:$E$692, E198) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30775,7 +30798,7 @@
         <v>280</v>
       </c>
       <c r="N199" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B199, $C$2:$C$692, C199, $D$2:$D$692, D199, $E$2:$E$692, E199) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O199" s="29"/>
@@ -30813,7 +30836,7 @@
         <v>55</v>
       </c>
       <c r="N200" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B200, $C$2:$C$692, C200, $D$2:$D$692, D200, $E$2:$E$692, E200) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30859,7 +30882,7 @@
         <v>650</v>
       </c>
       <c r="N201" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B201, $C$2:$C$692, C201, $D$2:$D$692, D201, $E$2:$E$692, E201) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P201" s="29"/>
@@ -30894,7 +30917,7 @@
       </c>
       <c r="J202" s="34"/>
       <c r="N202" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B202, $C$2:$C$692, C202, $D$2:$D$692, D202, $E$2:$E$692, E202) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -30940,7 +30963,7 @@
         <v>150</v>
       </c>
       <c r="N203" s="28" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B203, $C$2:$C$692, C203, $D$2:$D$692, D203, $E$2:$E$692, E203) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -30986,7 +31009,7 @@
         <v>250</v>
       </c>
       <c r="N204" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B204, $C$2:$C$692, C204, $D$2:$D$692, D204, $E$2:$E$692, E204) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -31022,7 +31045,7 @@
         <v>117</v>
       </c>
       <c r="N205" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B205, $C$2:$C$692, C205, $D$2:$D$692, D205, $E$2:$E$692, E205) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31056,7 +31079,7 @@
       </c>
       <c r="J206" s="34"/>
       <c r="N206" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B206, $C$2:$C$692, C206, $D$2:$D$692, D206, $E$2:$E$692, E206) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31102,7 +31125,7 @@
         <v>450</v>
       </c>
       <c r="N207" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B207, $C$2:$C$692, C207, $D$2:$D$692, D207, $E$2:$E$692, E207) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31148,7 +31171,7 @@
         <v>290</v>
       </c>
       <c r="N208" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B208, $C$2:$C$692, C208, $D$2:$D$692, D208, $E$2:$E$692, E208) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31184,7 +31207,7 @@
         <v>118</v>
       </c>
       <c r="N209" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B209, $C$2:$C$692, C209, $D$2:$D$692, D209, $E$2:$E$692, E209) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O209" s="29"/>
@@ -31231,7 +31254,7 @@
         <v>250</v>
       </c>
       <c r="N210" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B210, $C$2:$C$692, C210, $D$2:$D$692, D210, $E$2:$E$692, E210) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P210" s="29"/>
@@ -31278,7 +31301,7 @@
         <v>250</v>
       </c>
       <c r="N211" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B211, $C$2:$C$692, C211, $D$2:$D$692, D211, $E$2:$E$692, E211) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31324,7 +31347,7 @@
         <v>300</v>
       </c>
       <c r="N212" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B212, $C$2:$C$692, C212, $D$2:$D$692, D212, $E$2:$E$692, E212) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31370,7 +31393,7 @@
         <v>47900</v>
       </c>
       <c r="N213" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B213, $C$2:$C$692, C213, $D$2:$D$692, D213, $E$2:$E$692, E213) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O213" s="38" t="s">
@@ -31407,7 +31430,7 @@
       </c>
       <c r="J214" s="34"/>
       <c r="N214" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B214, $C$2:$C$692, C214, $D$2:$D$692, D214, $E$2:$E$692, E214) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31453,7 +31476,7 @@
         <v>816</v>
       </c>
       <c r="N215" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B215, $C$2:$C$692, C215, $D$2:$D$692, D215, $E$2:$E$692, E215) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31499,7 +31522,7 @@
         <v>650</v>
       </c>
       <c r="N216" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B216, $C$2:$C$692, C216, $D$2:$D$692, D216, $E$2:$E$692, E216) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O216" s="38" t="s">
@@ -31548,7 +31571,7 @@
         <v>495</v>
       </c>
       <c r="N217" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B217, $C$2:$C$692, C217, $D$2:$D$692, D217, $E$2:$E$692, E217) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O217" s="38" t="s">
@@ -31585,7 +31608,7 @@
       </c>
       <c r="J218" s="34"/>
       <c r="N218" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B218, $C$2:$C$692, C218, $D$2:$D$692, D218, $E$2:$E$692, E218) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31619,7 +31642,7 @@
       </c>
       <c r="J219" s="34"/>
       <c r="N219" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B219, $C$2:$C$692, C219, $D$2:$D$692, D219, $E$2:$E$692, E219) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31655,7 +31678,7 @@
         <v>118</v>
       </c>
       <c r="N220" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B220, $C$2:$C$692, C220, $D$2:$D$692, D220, $E$2:$E$692, E220) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31701,7 +31724,7 @@
         <v>480</v>
       </c>
       <c r="N221" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B221, $C$2:$C$692, C221, $D$2:$D$692, D221, $E$2:$E$692, E221) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31737,7 +31760,7 @@
         <v>55</v>
       </c>
       <c r="N222" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B222, $C$2:$C$692, C222, $D$2:$D$692, D222, $E$2:$E$692, E222) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31773,7 +31796,7 @@
         <v>117</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B223, $C$2:$C$692, C223, $D$2:$D$692, D223, $E$2:$E$692, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31819,7 +31842,7 @@
         <v>268</v>
       </c>
       <c r="N224" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B224, $C$2:$C$692, C224, $D$2:$D$692, D224, $E$2:$E$692, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31865,7 +31888,7 @@
         <v>320</v>
       </c>
       <c r="N225" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B225, $C$2:$C$692, C225, $D$2:$D$692, D225, $E$2:$E$692, E225) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31911,7 +31934,7 @@
         <v>448</v>
       </c>
       <c r="N226" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B226, $C$2:$C$692, C226, $D$2:$D$692, D226, $E$2:$E$692, E226) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31947,7 +31970,7 @@
         <v>117</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B227, $C$2:$C$692, C227, $D$2:$D$692, D227, $E$2:$E$692, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -31993,7 +32016,7 @@
         <v>300</v>
       </c>
       <c r="N228" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B228, $C$2:$C$692, C228, $D$2:$D$692, D228, $E$2:$E$692, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="38" t="s">
@@ -32031,7 +32054,7 @@
       </c>
       <c r="J229" s="34"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B229, $C$2:$C$692, C229, $D$2:$D$692, D229, $E$2:$E$692, E229) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32077,7 +32100,7 @@
         <v>360</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B230, $C$2:$C$692, C230, $D$2:$D$692, D230, $E$2:$E$692, E230) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O230" s="10"/>
@@ -32125,7 +32148,7 @@
         <v>651</v>
       </c>
       <c r="N231" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B231, $C$2:$C$692, C231, $D$2:$D$692, D231, $E$2:$E$692, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O231" s="10"/>
@@ -32173,7 +32196,7 @@
         <v>250</v>
       </c>
       <c r="N232" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B232, $C$2:$C$692, C232, $D$2:$D$692, D232, $E$2:$E$692, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32219,7 +32242,7 @@
         <v>650</v>
       </c>
       <c r="N233" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B233, $C$2:$C$692, C233, $D$2:$D$692, D233, $E$2:$E$692, E233) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O233"/>
@@ -32257,7 +32280,7 @@
         <v>118</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B234, $C$2:$C$692, C234, $D$2:$D$692, D234, $E$2:$E$692, E234) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32303,7 +32326,7 @@
         <v>260</v>
       </c>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B235, $C$2:$C$692, C235, $D$2:$D$692, D235, $E$2:$E$692, E235) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32349,7 +32372,7 @@
         <v>47480</v>
       </c>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B236, $C$2:$C$692, C236, $D$2:$D$692, D236, $E$2:$E$692, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32383,7 +32406,7 @@
       </c>
       <c r="J237" s="34"/>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B237, $C$2:$C$692, C237, $D$2:$D$692, D237, $E$2:$E$692, E237) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32429,7 +32452,7 @@
         <v>300</v>
       </c>
       <c r="N238" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B238, $C$2:$C$692, C238, $D$2:$D$692, D238, $E$2:$E$692, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32475,7 +32498,7 @@
         <v>340</v>
       </c>
       <c r="N239" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B239, $C$2:$C$692, C239, $D$2:$D$692, D239, $E$2:$E$692, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32521,7 +32544,7 @@
         <v>1800</v>
       </c>
       <c r="N240" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B240, $C$2:$C$692, C240, $D$2:$D$692, D240, $E$2:$E$692, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32555,7 +32578,7 @@
       </c>
       <c r="J241" s="34"/>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B241, $C$2:$C$692, C241, $D$2:$D$692, D241, $E$2:$E$692, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32594,7 +32617,7 @@
         <v>145</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B242, $C$2:$C$692, C242, $D$2:$D$692, D242, $E$2:$E$692, E242) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32631,7 +32654,7 @@
       <c r="L243" s="18"/>
       <c r="M243" s="18"/>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B243, $C$2:$C$692, C243, $D$2:$D$692, D243, $E$2:$E$692, E243) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O243" s="10"/>
@@ -32679,7 +32702,7 @@
         <v>500</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B244, $C$2:$C$692, C244, $D$2:$D$692, D244, $E$2:$E$692, E244) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O244" s="38" t="s">
@@ -32728,7 +32751,7 @@
         <v>300</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B245, $C$2:$C$692, C245, $D$2:$D$692, D245, $E$2:$E$692, E245) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32764,7 +32787,7 @@
         <v>117</v>
       </c>
       <c r="N246" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B246, $C$2:$C$692, C246, $D$2:$D$692, D246, $E$2:$E$692, E246) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32803,7 +32826,7 @@
       <c r="L247" s="18"/>
       <c r="M247" s="18"/>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B247, $C$2:$C$692, C247, $D$2:$D$692, D247, $E$2:$E$692, E247) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O247" s="10"/>
@@ -32841,7 +32864,7 @@
         <v>117</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B248, $C$2:$C$692, C248, $D$2:$D$692, D248, $E$2:$E$692, E248) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32887,7 +32910,7 @@
         <v>250</v>
       </c>
       <c r="N249" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B249, $C$2:$C$692, C249, $D$2:$D$692, D249, $E$2:$E$692, E249) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32923,7 +32946,7 @@
         <v>118</v>
       </c>
       <c r="N250" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B250, $C$2:$C$692, C250, $D$2:$D$692, D250, $E$2:$E$692, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -32969,7 +32992,7 @@
         <v>300</v>
       </c>
       <c r="N251" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B251, $C$2:$C$692, C251, $D$2:$D$692, D251, $E$2:$E$692, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33008,7 +33031,7 @@
       <c r="L252" s="18"/>
       <c r="M252" s="18"/>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B252, $C$2:$C$692, C252, $D$2:$D$692, D252, $E$2:$E$692, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="10"/>
@@ -33056,7 +33079,7 @@
         <v>400</v>
       </c>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B253, $C$2:$C$692, C253, $D$2:$D$692, D253, $E$2:$E$692, E253) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O253" s="10"/>
@@ -33094,7 +33117,7 @@
         <v>118</v>
       </c>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B254, $C$2:$C$692, C254, $D$2:$D$692, D254, $E$2:$E$692, E254) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33130,7 +33153,7 @@
         <v>117</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B255, $C$2:$C$692, C255, $D$2:$D$692, D255, $E$2:$E$692, E255) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="P255" s="29"/>
@@ -33170,7 +33193,7 @@
       <c r="L256" s="18"/>
       <c r="M256" s="18"/>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B256, $C$2:$C$692, C256, $D$2:$D$692, D256, $E$2:$E$692, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
       <c r="O256" s="10"/>
@@ -33213,7 +33236,7 @@
       <c r="L257" s="17"/>
       <c r="M257" s="17"/>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B257, $C$2:$C$692, C257, $D$2:$D$692, D257, $E$2:$E$692, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="9"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33247,7 +33270,7 @@
       </c>
       <c r="J258" s="34"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B258, $C$2:$C$692, C258, $D$2:$D$692, D258, $E$2:$E$692, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N298" si="10">IF(COUNTIFS( $B$2:$B$692, B258, $C$2:$C$692, C258, $D$2:$D$692, D258, $E$2:$E$692, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
@@ -33293,7 +33316,7 @@
         <v>260</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B259, $C$2:$C$692, C259, $D$2:$D$692, D259, $E$2:$E$692, E259) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O259" s="10"/>
@@ -33334,7 +33357,7 @@
       <c r="L260" s="18"/>
       <c r="M260" s="18"/>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B260, $C$2:$C$692, C260, $D$2:$D$692, D260, $E$2:$E$692, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O260" s="10"/>
@@ -33370,7 +33393,7 @@
       </c>
       <c r="J261" s="34"/>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B261, $C$2:$C$692, C261, $D$2:$D$692, D261, $E$2:$E$692, E261) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P261" s="29"/>
@@ -33417,7 +33440,7 @@
         <v>300</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B262, $C$2:$C$692, C262, $D$2:$D$692, D262, $E$2:$E$692, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33453,7 +33476,7 @@
         <v>117</v>
       </c>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B263, $C$2:$C$692, C263, $D$2:$D$692, D263, $E$2:$E$692, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33487,7 +33510,7 @@
       </c>
       <c r="J264" s="34"/>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B264, $C$2:$C$692, C264, $D$2:$D$692, D264, $E$2:$E$692, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O264" s="29"/>
@@ -33524,7 +33547,7 @@
         <v>117</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B265, $C$2:$C$692, C265, $D$2:$D$692, D265, $E$2:$E$692, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33560,7 +33583,7 @@
         <v>117</v>
       </c>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B266, $C$2:$C$692, C266, $D$2:$D$692, D266, $E$2:$E$692, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33596,7 +33619,7 @@
         <v>153</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B267, $C$2:$C$692, C267, $D$2:$D$692, D267, $E$2:$E$692, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33630,7 +33653,7 @@
       </c>
       <c r="J268" s="34"/>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B268, $C$2:$C$692, C268, $D$2:$D$692, D268, $E$2:$E$692, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="29"/>
@@ -33667,7 +33690,7 @@
         <v>117</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B269, $C$2:$C$692, C269, $D$2:$D$692, D269, $E$2:$E$692, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33713,7 +33736,7 @@
         <v>370</v>
       </c>
       <c r="N270" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B270, $C$2:$C$692, C270, $D$2:$D$692, D270, $E$2:$E$692, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P270" s="29"/>
@@ -33760,7 +33783,7 @@
         <v>235</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B271, $C$2:$C$692, C271, $D$2:$D$692, D271, $E$2:$E$692, E271) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33806,7 +33829,7 @@
         <v>285</v>
       </c>
       <c r="N272" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B272, $C$2:$C$692, C272, $D$2:$D$692, D272, $E$2:$E$692, E272) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33852,7 +33875,7 @@
         <v>726</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B273, $C$2:$C$692, C273, $D$2:$D$692, D273, $E$2:$E$692, E273) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33888,7 +33911,7 @@
         <v>117</v>
       </c>
       <c r="N274" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B274, $C$2:$C$692, C274, $D$2:$D$692, D274, $E$2:$E$692, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33924,7 +33947,7 @@
         <v>118</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B275, $C$2:$C$692, C275, $D$2:$D$692, D275, $E$2:$E$692, E275) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -33970,7 +33993,7 @@
         <v>300</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B276, $C$2:$C$692, C276, $D$2:$D$692, D276, $E$2:$E$692, E276) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O276" s="10"/>
@@ -34018,7 +34041,7 @@
         <v>275</v>
       </c>
       <c r="N277" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B277, $C$2:$C$692, C277, $D$2:$D$692, D277, $E$2:$E$692, E277) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O277" s="10"/>
@@ -34056,7 +34079,7 @@
         <v>117</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B278, $C$2:$C$692, C278, $D$2:$D$692, D278, $E$2:$E$692, E278) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34090,7 +34113,7 @@
       </c>
       <c r="J279" s="34"/>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B279, $C$2:$C$692, C279, $D$2:$D$692, D279, $E$2:$E$692, E279) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34124,7 +34147,7 @@
       </c>
       <c r="J280" s="34"/>
       <c r="N280" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B280, $C$2:$C$692, C280, $D$2:$D$692, D280, $E$2:$E$692, E280) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34170,7 +34193,7 @@
         <v>250</v>
       </c>
       <c r="N281" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B281, $C$2:$C$692, C281, $D$2:$D$692, D281, $E$2:$E$692, E281) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P281" s="29"/>
@@ -34205,7 +34228,7 @@
       </c>
       <c r="J282" s="34"/>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B282, $C$2:$C$692, C282, $D$2:$D$692, D282, $E$2:$E$692, E282) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34239,7 +34262,7 @@
       </c>
       <c r="J283" s="34"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B283, $C$2:$C$692, C283, $D$2:$D$692, D283, $E$2:$E$692, E283) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34285,7 +34308,7 @@
         <v>300</v>
       </c>
       <c r="N284" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B284, $C$2:$C$692, C284, $D$2:$D$692, D284, $E$2:$E$692, E284) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34319,7 +34342,7 @@
       </c>
       <c r="J285" s="34"/>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B285, $C$2:$C$692, C285, $D$2:$D$692, D285, $E$2:$E$692, E285) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="P285" s="29"/>
@@ -34356,7 +34379,7 @@
         <v>118</v>
       </c>
       <c r="N286" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B286, $C$2:$C$692, C286, $D$2:$D$692, D286, $E$2:$E$692, E286) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34392,7 +34415,7 @@
         <v>118</v>
       </c>
       <c r="N287" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B287, $C$2:$C$692, C287, $D$2:$D$692, D287, $E$2:$E$692, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34438,7 +34461,7 @@
         <v>300</v>
       </c>
       <c r="N288" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B288, $C$2:$C$692, C288, $D$2:$D$692, D288, $E$2:$E$692, E288) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34474,7 +34497,7 @@
         <v>118</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B289, $C$2:$C$692, C289, $D$2:$D$692, D289, $E$2:$E$692, E289) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34508,7 +34531,7 @@
       </c>
       <c r="J290" s="34"/>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B290, $C$2:$C$692, C290, $D$2:$D$692, D290, $E$2:$E$692, E290) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34542,7 +34565,7 @@
       </c>
       <c r="J291" s="34"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B291, $C$2:$C$692, C291, $D$2:$D$692, D291, $E$2:$E$692, E291) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34576,7 +34599,7 @@
       </c>
       <c r="J292" s="34"/>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B292, $C$2:$C$692, C292, $D$2:$D$692, D292, $E$2:$E$692, E292) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34622,7 +34645,7 @@
         <v>250</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B293, $C$2:$C$692, C293, $D$2:$D$692, D293, $E$2:$E$692, E293) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34658,7 +34681,7 @@
         <v>55</v>
       </c>
       <c r="N294" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B294, $C$2:$C$692, C294, $D$2:$D$692, D294, $E$2:$E$692, E294) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34697,7 +34720,7 @@
       <c r="L295" s="27"/>
       <c r="M295" s="27"/>
       <c r="N295" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B295, $C$2:$C$692, C295, $D$2:$D$692, D295, $E$2:$E$692, E295) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O295" s="29"/>
@@ -34738,7 +34761,7 @@
       <c r="L296" s="27"/>
       <c r="M296" s="27"/>
       <c r="N296" s="29" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B296, $C$2:$C$692, C296, $D$2:$D$692, D296, $E$2:$E$692, E296) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
       <c r="O296" s="29"/>
@@ -34776,7 +34799,7 @@
         <v>117</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B297, $C$2:$C$692, C297, $D$2:$D$692, D297, $E$2:$E$692, E297) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
@@ -34814,7 +34837,7 @@
         <v>295</v>
       </c>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$692, B298, $C$2:$C$692, C298, $D$2:$D$692, D298, $E$2:$E$692, E298) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="10"/>
         <v>Unique</v>
       </c>
     </row>
